--- a/templates_xlsx/extraction_workbook_B.xlsx
+++ b/templates_xlsx/extraction_workbook_B.xlsx
@@ -1231,12 +1231,12 @@
     </comment>
     <comment ref="AB1" authorId="0" shapeId="0">
       <text>
-        <t>Audit why each named immune candidate enters the map; include regardless of statistical significance.
+        <t>全文页码/节/表/补充材料定位 (same-name legacy field, mapped to reports)
 Type: array
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
 Multiple values: separate with "; "
-Source: new_operational_fields_not_in_legacy_61["measurements.candidate_in_original_aims_methods / source_locator"]</t>
+Source: legacy_61_fields["source_locator"] (same name, other table)</t>
       </text>
     </comment>
     <comment ref="AC1" authorId="0" shapeId="0">
@@ -1269,20 +1269,20 @@
     </comment>
     <comment ref="AF1" authorId="0" shapeId="0">
       <text>
-        <t>No definition in data_dictionary.json (see extraction_manual.md); field name is self-describing.
+        <t>Explicit assay-level tested feature space/denominator: definition plus count and unit, including platform and QC/filtering rules.
 Type: integer_or_missing_code
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
-Source: NONE</t>
+Source: new_operational_fields_not_in_legacy_61["measurements.tested_universe / n / unit"]</t>
       </text>
     </comment>
     <comment ref="AG1" authorId="0" shapeId="0">
       <text>
-        <t>No definition in data_dictionary.json (see extraction_manual.md); field name is self-describing.
+        <t>Explicit assay-level tested feature space/denominator: definition plus count and unit, including platform and QC/filtering rules.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
-Source: NONE</t>
+Source: new_operational_fields_not_in_legacy_61["measurements.tested_universe / n / unit"]</t>
       </text>
     </comment>
     <comment ref="AH1" authorId="0" shapeId="0">
@@ -1363,12 +1363,12 @@
     </comment>
     <comment ref="AP1" authorId="0" shapeId="0">
       <text>
-        <t>No definition in data_dictionary.json (see extraction_manual.md); field name is self-describing.
+        <t>Audit why each named immune candidate enters the map; include regardless of statistical significance.
 Type: array
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
 Multiple values: separate with "; "
-Source: NONE</t>
+Source: new_operational_fields_not_in_legacy_61["measurements.candidate_in_original_aims_methods / source_locator"]</t>
       </text>
     </comment>
     <comment ref="AQ1" authorId="0" shapeId="0">
@@ -3007,7 +3007,7 @@
     <row r="84">
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>reports.reference_id, reports.title, reports.authors, reports.year, reports.url, reports.version_label, reports.screening_A, reports.screening_B, reports.consensus_screening_decision, reports.primary_fulltext_exclusion_reason, reports.reviewer_notes, reports.author_stated_use, cohorts.cohort_label, cohorts.cohort_notes, report_cohort_links.report_specific_population, report_cohort_links.link_notes, sample_sets.group_condition, sample_sets.intervention_phase, sample_sets.assay_platform, sample_sets.n_aliquots, sample_sets.age_sex_stratum, sample_sets.sample_notes, measurements.effect_measure, measurements.effect_value, measurements.effect_unit, measurements.result_direction, measurements.reported_feature_count, measurements.measurement_notes, measurements.tested_universe_n, measurements.tested_universe_unit, measurements.candidate_source_locator, measurements.figure_panel_locator, precision_validation.evidence_notes, extraction_provenance.recorded_at, extraction_provenance.provenance_notes, study_families.study_label, study_families.registry_ids, study_families.study_notes</t>
+          <t>reports.reference_id, reports.title, reports.authors, reports.year, reports.url, reports.version_label, reports.screening_A, reports.screening_B, reports.consensus_screening_decision, reports.primary_fulltext_exclusion_reason, reports.reviewer_notes, reports.author_stated_use, cohorts.cohort_label, cohorts.cohort_notes, report_cohort_links.report_specific_population, report_cohort_links.link_notes, sample_sets.group_condition, sample_sets.intervention_phase, sample_sets.assay_platform, sample_sets.n_aliquots, sample_sets.age_sex_stratum, sample_sets.sample_notes, measurements.effect_measure, measurements.effect_value, measurements.effect_unit, measurements.result_direction, measurements.reported_feature_count, measurements.measurement_notes, measurements.figure_panel_locator, precision_validation.evidence_notes, extraction_provenance.recorded_at, extraction_provenance.provenance_notes, study_families.study_label, study_families.registry_ids, study_families.study_notes</t>
         </is>
       </c>
     </row>
@@ -9344,12 +9344,12 @@
       <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr">
         <is>
-          <t>Audit why each named immune candidate enters the map; include regardless of statistical significance.</t>
+          <t>全文页码/节/表/补充材料定位 (same-name legacy field, mapped to reports)</t>
         </is>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>new_operational_fields_not_in_legacy_61["measurements.candidate_in_original_aims_methods / source_locator"]</t>
+          <t>legacy_61_fields["source_locator"] (same name, other table)</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr"/>
@@ -9556,12 +9556,12 @@
       <c r="J111" s="4" t="inlineStr"/>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>No definition in data_dictionary.json (see extraction_manual.md); field name is self-describing.</t>
+          <t>Explicit assay-level tested feature space/denominator: definition plus count and unit, including platform and QC/filtering rules.</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>new_operational_fields_not_in_legacy_61["measurements.tested_universe / n / unit"]</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr"/>
@@ -9607,12 +9607,12 @@
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr">
         <is>
-          <t>No definition in data_dictionary.json (see extraction_manual.md); field name is self-describing.</t>
+          <t>Explicit assay-level tested feature space/denominator: definition plus count and unit, including platform and QC/filtering rules.</t>
         </is>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>new_operational_fields_not_in_legacy_61["measurements.tested_universe / n / unit"]</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr"/>
@@ -10090,12 +10090,12 @@
       <c r="J121" s="4" t="inlineStr"/>
       <c r="K121" s="4" t="inlineStr">
         <is>
-          <t>No definition in data_dictionary.json (see extraction_manual.md); field name is self-describing.</t>
+          <t>Audit why each named immune candidate enters the map; include regardless of statistical significance.</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>new_operational_fields_not_in_legacy_61["measurements.candidate_in_original_aims_methods / source_locator"]</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr"/>
@@ -15173,19 +15173,19 @@
       <formula1>AND(A2&lt;&gt;"NR",A2&lt;&gt;"NA",A2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="publication_status" prompt="peer_reviewed_version_of_record; peer_reviewed_online_first; preprint; conference_abstract; protocol; editorial_or_commentary; correction; retraction; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_repo_publication_status</formula1>
+      <formula1>voc_repo_publication_status</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="scope_stream" prompt="A_core_acute; B_support_repeated_bouts; background_context; excluded; awaiting_classification; not_retrieved; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_repo_scope_stream</formula1>
+      <formula1>voc_repo_scope_stream</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="immune_link" prompt="Choose from codes sheet (immune_link).  Multi: &quot;; &quot;" type="list" errorStyle="warning">
-      <formula1>=voc_repo_immune_link</formula1>
+      <formula1>voc_repo_immune_link</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="consensus_screening_decision" prompt="ADVANCE; EXCLUDE_TA; FRONTIER_PREPRINT; AWAITING_CLASSIFICATION; INCLUDE_A; INCLUDE_B; INCLUDE_A_AND_B; EXCLUDE_FT; NOT_RETRIEVED; AWAITING_TRANSLATION; DUPLICATE_RECORD; DUPLICATE_VERSION; NR; NA; UNCLEAR" type="list" errorStyle="warning">
-      <formula1>=voc_repo_consensus_screening_decision</formula1>
+      <formula1>voc_repo_consensus_screening_decision</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="primary_fulltext_exclusion_reas…" prompt="Choose from codes sheet (fulltext_exclusion_codes.json hierarchy)." type="list" errorStyle="warning">
-      <formula1>=voc_repo_primary_fulltext_exclusion_reason</formula1>
+      <formula1>voc_repo_primary_fulltext_exclusion_reason</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15362,7 +15362,7 @@
       <formula1>IF(ISNUMBER(E2),AND(E2&gt;=0,E2=INT(E2)),OR(E2="NR",E2="NA",E2="UNCLEAR"))</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="scope_streams" prompt="A_core_acute; B_support_repeated_bouts; background_context; excluded; awaiting_classification; not_retrieved  Multi: &quot;; &quot;" type="list" errorStyle="warning">
-      <formula1>=voc_repo_scope_streams</formula1>
+      <formula1>voc_repo_scope_streams</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15635,10 +15635,10 @@
       <formula1>AND(D2&lt;&gt;"NR",D2&lt;&gt;"NA",D2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="sample_role" prompt="pre_exercise_baseline; during_exercise; immediate_post; recovery_post; nonexercise_control; matched_control; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_samp_sample_role</formula1>
+      <formula1>voc_samp_sample_role</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="time_bin" prompt="pre_exercise_baseline; during; 0_to_&lt;30min; 30min_to_&lt;3h; 3h_to_&lt;24h; 24h_to_72h_inclusive; &gt;72h; matched_control_time; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_samp_time_bin</formula1>
+      <formula1>voc_samp_time_bin</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="n_participants" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(T2),AND(T2&gt;=0,T2=INT(T2)),OR(T2="NR",T2="NA",T2="UNCLEAR"))</formula1>
@@ -15656,13 +15656,13 @@
       <formula1>IF(ISNUMBER(X2),AND(X2&gt;=0,X2=INT(X2)),OR(X2="NR",X2="NA",X2="UNCLEAR"))</formula1>
     </dataValidation>
     <dataValidation sqref="AK2:AK1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="participant_linkage" prompt="same_participants_identified; same_participants_aggregate_pairing_documented; some_participant_overlap; different_participants; not_reported; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_samp_participant_linkage</formula1>
+      <formula1>voc_samp_participant_linkage</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="n_donors" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(AL2),AND(AL2&gt;=0,AL2=INT(AL2)),OR(AL2="NR",AL2="NA",AL2="UNCLEAR"))</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="donor_count_basis" prompt="unique_human_donors; unique_participants_equivalent; pooled_or_composite_donor_material; donor_identity_not_resolved; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_samp_donor_count_basis</formula1>
+      <formula1>voc_samp_donor_count_basis</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16034,16 +16034,16 @@
       <formula1>AND(E2&lt;&gt;"NR",E2&lt;&gt;"NA",E2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="biological_level" prompt="cell_count_or_subset; cellular_function; RNA_mRNA; RNA_miRNA; RNA_lncRNA; RNA_circRNA; RNA_other; protein; cytokine_or_immune_mediator; metabolite; lipid; DNA_methylation; chromatin_accessibility; other; NR; NA; UNCLEAR" type="list" errorStyle="warning">
-      <formula1>=voc_meas_biological_level</formula1>
+      <formula1>voc_meas_biological_level</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="omics_integration" prompt="single_omics; multiple_omics_parallel; integrated_multiomics; not_omics; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_omics_integration</formula1>
+      <formula1>voc_meas_omics_integration</formula1>
     </dataValidation>
     <dataValidation sqref="Z2:Z1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="reported_feature_count" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(Z2),AND(Z2&gt;=0,Z2=INT(Z2)),OR(Z2="NR",Z2="NA",Z2="UNCLEAR"))</formula1>
     </dataValidation>
     <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="record_type" prompt="assay_universe_summary; named_immune_candidate; reported_result_summary" type="list" errorStyle="stop">
-      <formula1>=voc_meas_record_type</formula1>
+      <formula1>voc_meas_record_type</formula1>
     </dataValidation>
     <dataValidation sqref="AF2:AF1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="tested_universe_n" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(AF2),AND(AF2&gt;=0,AF2=INT(AF2)),OR(AF2="NR",AF2="NA",AF2="UNCLEAR"))</formula1>
@@ -16052,22 +16052,22 @@
       <formula1>IF(ISNUMBER(AI2),AND(AI2&gt;=0,AI2=INT(AI2)),OR(AI2="NR",AI2="NA",AI2="UNCLEAR"))</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_selection_rule" prompt="all_named_immune_candidates_from_original_aims_methods_regardless_of_significance; complete_targeted_panel; author_reported_feature_set; other_source_defined_rule; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_candidate_selection_rule</formula1>
+      <formula1>voc_meas_candidate_selection_rule</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_selection_basis" prompt="original_aims; original_methods; registered_protocol_or_analysis_plan; supplement; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_candidate_selection_basis</formula1>
+      <formula1>voc_meas_candidate_selection_basis</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_prespecification_stat…" prompt="registered_protocol_or_analysis_plan; stated_in_original_aims_or_methods_no_registration_required; posthoc_or_results_only; timing_unclear; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_candidate_prespecification_status</formula1>
+      <formula1>voc_meas_candidate_prespecification_status</formula1>
     </dataValidation>
     <dataValidation sqref="AQ2:AQ1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="supplement_availability" prompt="accessible; linked_but_not_accessible; not_listed; not_checked; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_supplement_availability</formula1>
+      <formula1>voc_meas_supplement_availability</formula1>
     </dataValidation>
     <dataValidation sqref="AS2:AS1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="result_status" prompt="reported_significant; explicitly_reported_non_significant_or_null; named_candidate_result_not_located; assay_universe_only_no_candidate_result_reported; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_result_status</formula1>
+      <formula1>voc_meas_result_status</formula1>
     </dataValidation>
     <dataValidation sqref="AT2:AT1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="effect_value_source" prompt="reported_main_text_or_table; reported_supplement; author_provided; digitized_from_figure; not_reported; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_meas_effect_value_source</formula1>
+      <formula1>voc_meas_effect_value_source</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16247,25 +16247,25 @@
       <formula1>AND(E2&lt;&gt;"NR",E2&lt;&gt;"NA",E2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="precision_domain" prompt="analytical_reliability; temporal_validity; immune_specificity; individualization; functional_clinical_linkage; independent_validation_and_use; feasibility" type="list" errorStyle="stop">
-      <formula1>=voc_prec_precision_domain</formula1>
+      <formula1>voc_prec_precision_domain</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="evidence_state" prompt="evidence_present; measured_null; not_demonstrated; not_reported; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_prec_evidence_state</formula1>
+      <formula1>voc_prec_evidence_state</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="relationship_tags" prompt="Choose from codes sheet (relationship_tags).  Multi: &quot;; &quot;" type="list" errorStyle="warning">
-      <formula1>=voc_prec_relationship_tags</formula1>
+      <formula1>voc_prec_relationship_tags</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="clinical_endpoint" prompt="none_reported; self_reported_symptoms; clinician_defined_syndrome; pathogen_confirmed_infection; other_clinical_endpoint; NR; NA; UNCLEAR" type="list" errorStyle="warning">
-      <formula1>=voc_prec_clinical_endpoint</formula1>
+      <formula1>voc_prec_clinical_endpoint</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="intended_use" prompt="Choose from codes sheet (intended_use)." type="list" errorStyle="stop">
-      <formula1>=voc_prec_intended_use</formula1>
+      <formula1>voc_prec_intended_use</formula1>
     </dataValidation>
     <dataValidation sqref="V2:V1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="linkage_subtype" prompt="direct_functional_evidence; functional_assay_association; clinical_symptom_outcome; clinician_defined_outcome; pathogen_confirmed_outcome; combined_functional_and_clinical; no_linkage_evidence; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_prec_linkage_subtype</formula1>
+      <formula1>voc_prec_linkage_subtype</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="validation_use_subtype" prompt="independent_cohort_replication; independent_external_model_validation; internal_validation; prospective_use_or_impact_validation; implementation_or_field_use_validation; no_validation_or_use_test; NR; NA; UNCLEAR" type="list" errorStyle="stop">
-      <formula1>=voc_prec_validation_use_subtype</formula1>
+      <formula1>voc_prec_validation_use_subtype</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates_xlsx/extraction_workbook_B.xlsx
+++ b/templates_xlsx/extraction_workbook_B.xlsx
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>scripts/build_workbooks.py v1.0.0</t>
+          <t>scripts/build_workbooks.py v1.1.0</t>
         </is>
       </c>
     </row>

--- a/templates_xlsx/extraction_workbook_B.xlsx
+++ b/templates_xlsx/extraction_workbook_B.xlsx
@@ -23,48 +23,54 @@
     <definedName name="voc_repo_publication_status">'codes'!$A$2:$A$13</definedName>
     <definedName name="voc_repo_scope_stream">'codes'!$C$2:$C$9</definedName>
     <definedName name="voc_repo_immune_link">'codes'!$E$2:$E$12</definedName>
-    <definedName name="voc_repo_consensus_screening_decision">'codes'!$G$2:$G$16</definedName>
+    <definedName name="voc_repo_consensus_screening_decision">'codes'!$G$2:$G$19</definedName>
     <definedName name="voc_repo_primary_fulltext_exclusion_reason">'codes'!$I$2:$I$12</definedName>
     <definedName name="voc_repo_author_window_interpretation">'codes'!$K$2:$K$8</definedName>
-    <definedName name="voc_coho_adult_stratum_separable">'codes'!$M$2:$M$8</definedName>
-    <definedName name="voc_coho_older_adult_subgroup">'codes'!$O$2:$O$7</definedName>
-    <definedName name="voc_repo_scope_streams">'codes'!$Q$2:$Q$9</definedName>
-    <definedName name="voc_samp_sample_role">'codes'!$S$2:$S$11</definedName>
-    <definedName name="voc_samp_time_bin">'codes'!$U$2:$U$12</definedName>
-    <definedName name="voc_samp_participant_linkage">'codes'!$W$2:$W$8</definedName>
-    <definedName name="voc_samp_donor_count_basis">'codes'!$Y$2:$Y$8</definedName>
-    <definedName name="voc_samp_within_organising_window">'codes'!$AA$2:$AA$9</definedName>
-    <definedName name="voc_meas_biological_level">'codes'!$AC$2:$AC$18</definedName>
-    <definedName name="voc_meas_omics_integration">'codes'!$AE$2:$AE$8</definedName>
-    <definedName name="voc_meas_result_direction">'codes'!$AG$2:$AG$8</definedName>
-    <definedName name="voc_meas_record_type">'codes'!$AI$2:$AI$4</definedName>
-    <definedName name="voc_meas_candidate_selection_rule">'codes'!$AK$2:$AK$8</definedName>
-    <definedName name="voc_meas_candidate_selection_basis">'codes'!$AM$2:$AM$9</definedName>
-    <definedName name="voc_meas_candidate_prespecification_status">'codes'!$AO$2:$AO$8</definedName>
-    <definedName name="voc_meas_supplement_availability">'codes'!$AQ$2:$AQ$8</definedName>
-    <definedName name="voc_meas_result_status">'codes'!$AS$2:$AS$8</definedName>
-    <definedName name="voc_meas_effect_value_source">'codes'!$AU$2:$AU$8</definedName>
-    <definedName name="voc_meas_marker_family">'codes'!$AW$2:$AW$18</definedName>
-    <definedName name="voc_meas_digitization_check">'codes'!$AY$2:$AY$8</definedName>
-    <definedName name="voc_prec_precision_domain">'codes'!$BA$2:$BA$8</definedName>
-    <definedName name="voc_prec_evidence_state">'codes'!$BC$2:$BC$7</definedName>
-    <definedName name="voc_prec_relationship_tags">'codes'!$BE$2:$BE$15</definedName>
-    <definedName name="voc_prec_clinical_endpoint">'codes'!$BG$2:$BG$9</definedName>
-    <definedName name="voc_prec_intended_use">'codes'!$BI$2:$BI$15</definedName>
-    <definedName name="voc_prec_linkage_subtype">'codes'!$BK$2:$BK$11</definedName>
-    <definedName name="voc_prec_validation_use_subtype">'codes'!$BM$2:$BM$10</definedName>
-    <definedName name="voc_prec_validation_split">'codes'!$BO$2:$BO$8</definedName>
-    <definedName name="voc_missing_codes">'codes'!$BQ$2:$BQ$4</definedName>
-    <definedName name="voc_missing_codes_table">'codes'!$BQ$2:$BR$4</definedName>
+    <definedName name="voc_coho_training_status">'codes'!$M$2:$M$10</definedName>
+    <definedName name="voc_coho_adult_stratum_separable">'codes'!$O$2:$O$8</definedName>
+    <definedName name="voc_coho_older_adult_subgroup">'codes'!$Q$2:$Q$7</definedName>
+    <definedName name="voc_repo_scope_streams">'codes'!$S$2:$S$9</definedName>
+    <definedName name="voc_samp_exercise_mode">'codes'!$U$2:$U$10</definedName>
+    <definedName name="voc_samp_sample_role">'codes'!$W$2:$W$13</definedName>
+    <definedName name="voc_samp_time_unit">'codes'!$Y$2:$Y$7</definedName>
+    <definedName name="voc_samp_time_bin">'codes'!$AA$2:$AA$12</definedName>
+    <definedName name="voc_samp_matrix">'codes'!$AC$2:$AC$16</definedName>
+    <definedName name="voc_samp_participant_linkage">'codes'!$AE$2:$AE$8</definedName>
+    <definedName name="voc_samp_donor_count_basis">'codes'!$AG$2:$AG$8</definedName>
+    <definedName name="voc_samp_within_organising_window">'codes'!$AI$2:$AI$9</definedName>
+    <definedName name="voc_meas_biological_level">'codes'!$AK$2:$AK$18</definedName>
+    <definedName name="voc_meas_omics_integration">'codes'!$AM$2:$AM$8</definedName>
+    <definedName name="voc_meas_result_direction">'codes'!$AO$2:$AO$8</definedName>
+    <definedName name="voc_meas_record_type">'codes'!$AQ$2:$AQ$4</definedName>
+    <definedName name="voc_meas_candidate_selection_rule">'codes'!$AS$2:$AS$9</definedName>
+    <definedName name="voc_meas_candidate_selection_basis">'codes'!$AU$2:$AU$10</definedName>
+    <definedName name="voc_meas_candidate_prespecification_status">'codes'!$AW$2:$AW$8</definedName>
+    <definedName name="voc_meas_supplement_availability">'codes'!$AY$2:$AY$8</definedName>
+    <definedName name="voc_meas_result_status">'codes'!$BA$2:$BA$8</definedName>
+    <definedName name="voc_meas_effect_value_source">'codes'!$BC$2:$BC$8</definedName>
+    <definedName name="voc_meas_marker_family">'codes'!$BE$2:$BE$19</definedName>
+    <definedName name="voc_meas_digitization_check">'codes'!$BG$2:$BG$8</definedName>
+    <definedName name="voc_prec_precision_domain">'codes'!$BI$2:$BI$8</definedName>
+    <definedName name="voc_prec_evidence_state">'codes'!$BK$2:$BK$7</definedName>
+    <definedName name="voc_prec_relationship_tags">'codes'!$BM$2:$BM$15</definedName>
+    <definedName name="voc_prec_clinical_endpoint">'codes'!$BO$2:$BO$9</definedName>
+    <definedName name="voc_prec_intended_use">'codes'!$BQ$2:$BQ$15</definedName>
+    <definedName name="voc_prec_linkage_subtype">'codes'!$BS$2:$BS$11</definedName>
+    <definedName name="voc_prec_validation_use_subtype">'codes'!$BU$2:$BU$10</definedName>
+    <definedName name="voc_prec_validation_split">'codes'!$BW$2:$BW$8</definedName>
+    <definedName name="voc_prec_marker_family">'codes'!$BY$2:$BY$19</definedName>
+    <definedName name="voc_stud_design">'codes'!$CA$2:$CA$13</definedName>
+    <definedName name="voc_missing_codes">'codes'!$CC$2:$CC$4</definedName>
+    <definedName name="voc_missing_codes_table">'codes'!$CC$2:$CD$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'reports'!$A$1:$X$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'cohorts'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'report_cohort_links'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'sample_sets'!$A$1:$AQ$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'measurements'!$A$1:$BE$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'precision_validation'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'precision_validation'!$A$1:$Y$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'extraction_provenance'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'study_families'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'data_dictionary'!$A$1:$O$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'data_dictionary'!$A$1:$O$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -244,7 +250,7 @@
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Project reference identifier: the record_id of the retained deduplicated screening record, or for pilot items the restart ledger ID (e.g. R59). Text; never reused.
+        <t>Project reference identifier: the record_id of the retained deduplicated screening record, or for pilot items the restart ledger ID (e.g. R59). Version rows of the same report add a suffix (R01-V1, R01-V2). Text; never reused.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -307,7 +313,7 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>同行评审/预印本/会议摘要/更正/撤稿
+        <t>同行评审/预印本/会议摘要/更正/撤稿 v3.1: peer-review/version status only; short-format article type goes to version_label (controlled_vocabulary_definitions.publication_status).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -317,7 +323,7 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>在线首发与当前版本日期
+        <t>在线首发与当前版本日期 v3.1: ISO 8601 (YYYY-MM-DD) online publication date of the version consulted; else issue date; else accepted date with flag ACCEPTED_DATE_USED in reviewer_notes.
 Type: object
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -326,7 +332,7 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Version label as published (e.g. version of record, online first, bioRxiv v2, correction notice); paired with version_date.
+        <t>Version label and article type as published (e.g. "version of record; short communication", "bioRxiv v2", "Did You Know? (peer reviewed)", correction notice); paired with version_date.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -385,7 +391,7 @@
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Full-text screening disposition of human Reviewer A, copied verbatim from Reviewer A's locked screening workbook / merge output (04_screening/screening_log_template.json field_schema.screening_dispositions, FT stage). A reviewer decision, not Core A membership. Renamed in v3 from screening_A (not legacy-61).
+        <t>Full-text screening disposition of human Reviewer A, copied verbatim from Reviewer A's locked screening workbook / merge output (04_screening/screening_log_template.json field_schema.screening_dispositions, FT stage). A reviewer decision, not Core A membership. Renamed in v3 from screening_A (not legacy-61). Copy-only; null when no screening record exists.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -394,7 +400,7 @@
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>Full-text screening disposition of human Reviewer B, copied verbatim from Reviewer B's locked screening workbook / merge output (screening_dispositions, FT stage). A reviewer decision, not Support B membership. Renamed in v3 from screening_B (not legacy-61).
+        <t>Full-text screening disposition of human Reviewer B, copied verbatim from Reviewer B's locked screening workbook / merge output (screening_dispositions, FT stage). A reviewer decision, not Support B membership. Renamed in v3 from screening_B (not legacy-61). Copy-only; null when no screening record exists.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -403,17 +409,17 @@
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>Reconciled full-text disposition (screening_log_template full_text.reconciliation.final_disposition): INCLUDE_A, INCLUDE_B, INCLUDE_A_AND_B, EXCLUDE_FT or an administrative status; maps to scope_stream through vocabulary_crosswalks.scope_stream.from_screening_disposition.
+        <t>Reconciled full-text disposition (screening_log_template full_text.reconciliation.final_disposition): INCLUDE_A, INCLUDE_B, INCLUDE_A_AND_B, EXCLUDE_FT, RETAIN_BACKGROUND or another administrative status; maps to scope_stream through vocabulary_crosswalks.scope_stream.from_screening_disposition. Copy-only; null when no screening record exists.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
-Allowed (warning (cross-file list)): ADVANCE | EXCLUDE_TA | FRONTIER_PREPRINT | AWAITING_CLASSIFICATION | INCLUDE_A | INCLUDE_B | INCLUDE_A_AND_B | EXCLUDE_FT | NOT_RETRIEVED | AWAITING_TRANSLATION | DUPLICATE_RECORD | DUPLICATE_VERSION | NR | NA | UNCLEAR
+Allowed (warning (cross-file list)): ADVANCE_TO_ABSTRACT | EXCLUDE_TITLE | ADVANCE | EXCLUDE_TA | FRONTIER_PREPRINT | AWAITING_CLASSIFICATION | INCLUDE_A | INCLUDE_B | INCLUDE_A_AND_B | EXCLUDE_FT | RETAIN_BACKGROUND | NOT_RETRIEVED | AWAITING_TRANSLATION | DUPLICATE_RECORD | DUPLICATE_VERSION | NR | NA | UNCLEAR
 Source: new_operational_fields_not_in_legacy_61["reports.consensus_screening_decision"]</t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Canonical v3 field for the single primary full-text exclusion code (first established FT01-FT08 code; 04_screening/fulltext_exclusion_codes.json). Null unless consensus_screening_decision = EXCLUDE_FT; administrative statuses take no code. Supersedes the legacy column reports.exclusion_reason (deprecated alias, kept null).
+        <t>Canonical v3 field for the single primary full-text exclusion code (first established FT01-FT08 code; 04_screening/fulltext_exclusion_codes.json). Null unless consensus_screening_decision = EXCLUDE_FT; administrative statuses (including RETAIN_BACKGROUND) take no code. Supersedes the legacy column reports.exclusion_reason (deprecated alias, kept null). Copy-only.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -441,7 +447,7 @@
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued, "; "): whether the report uses the open-window term, invokes immunosuppression or susceptibility without the term, interprets changes as redistribution, or offers no window interpretation; plus the locator(s) of the source passage. Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.
+        <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued and exhaustive, "; "): authors' own voice only (adopted introduction rationale, discussion, conclusions); one locator per value written "value: locator" (analysis_unit_rules.author_window_interpretation). Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.
 Type: multi_enum (array)
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -452,7 +458,7 @@
     </comment>
     <comment ref="X1" authorId="0" shapeId="0">
       <text>
-        <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued, "; "): whether the report uses the open-window term, invokes immunosuppression or susceptibility without the term, interprets changes as redistribution, or offers no window interpretation; plus the locator(s) of the source passage. Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.
+        <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued and exhaustive, "; "): authors' own voice only (adopted introduction rationale, discussion, conclusions); one locator per value written "value: locator" (analysis_unit_rules.author_window_interpretation). Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.
 Type: array
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -508,7 +514,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>招募人数
+        <t>招募人数 v3.1: people enrolled before any exclusion in the cohort as the report defines it; when several candidate numbers exist, record the pre-exclusion enrolment and list the others in cohort_notes.
 Type: integer_or_missing_code
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
@@ -526,10 +532,11 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>未训练/休闲/训练/精英
+        <t>未训练/休闲/训练/精英 v3.1: controlled_vocabulary.training_status.
 Type: enum_or_text
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
+Allowed (warning (free text allowed)): untrained_or_sedentary | recreationally_active | trained | elite_or_professional | mixed_training_status | other | NR | NA | UNCLEAR
 Source: legacy_61_fields["training_status"] (population)</t>
       </text>
     </comment>
@@ -544,7 +551,7 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Free-text notes on the cohort (recruitment source, overlap reasoning with other reports, separable strata) with locators.
+        <t>Free-text notes on the cohort (recruitment source, alternative enrolment figures, overlap reasoning with other reports, separable strata, age-rule derivation) with locators.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -553,7 +560,7 @@
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Age range and summary exactly as reported (e.g. "18-35 y; mean 24.1 (SD 3.2)"), including any older-adult threshold used by the authors; NR if not reported (unreported age remains awaiting classification at screening, not FT03).
+        <t>Age range and summary exactly as reported (e.g. "18-35 y; mean 24.1 (SD 3.2)"), including any older-adult threshold used by the authors; NR if not reported (unreported or non-qualifying age remains awaiting classification at screening, not FT03; age rule in analysis_unit_rules.population).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -562,7 +569,7 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Adult-population status (controlled_vocabulary.adult_stratum_separable): all participants &gt;= 18 y; mixed-age cohort with a separable adult stratum (eligible; chart that stratum only); mixed-age cohort without a separable adult stratum, or all &lt; 18 y (FT03; appears only in boundary/pilot records).
+        <t>Adult-population status (controlled_vocabulary.adult_stratum_separable) under the age rule (analysis_unit_rules.population: explicit range/minimum &gt;= 18 y or mean - 2*SD &gt;= 18 y): all participants &gt;= 18 y; mixed-age cohort with a separable adult stratum (eligible; chart that stratum only); mixed-age cohort without a separable adult stratum, or all &lt; 18 y (FT03; only when &lt; 18 y participation is stated); UNCLEAR when the rule cannot be applied.
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -628,7 +635,7 @@
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>该分析有效独立受试者数
+        <t>该分析有效独立受试者数 v3.1: unique participants analysed for the primary immune outcome of this report-cohort link (the immune outcome named first in the aims, else the first immune result reported); other denominators (other outcomes, platforms, subgroups) go to link_notes and to sample_sets.n_participants.
 Type: integer_or_missing_code
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
@@ -646,7 +653,7 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Free-text justification of the report-study-cohort link (shared registry ID, identical baseline table, author statement) with locators.
+        <t>Free-text justification of the report-study-cohort link (shared registry ID, identical baseline table, author statement) and the other denominators of this report (outcome-, platform- or subgroup-specific n) with locators.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -676,7 +683,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Primary key of sample_sets (one group × assay/matrix × exact timepoint sample set).
+        <t>Primary key of sample_sets (one cohort × group/arm × matrix × time point as sampled in the Methods (whether or not a result is reported for that combination); assay platforms are listed in assay_platform ("; "-separated). Split by platform only when the report gives a platform-specific n that differs between platforms at that time point; split by analysis subgroup only when subgroup n and subgroup results are reported; control-arm time points get their own rows.).
 Type: identifier
 Missing values: forbidden (identifier)
 Excel format: Text (@)
@@ -730,10 +737,11 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>耐力/抗阻/混合/比赛
+        <t>耐力/抗阻/混合/比赛 v3.1: controlled_vocabulary.exercise_mode (competition coded by its mode).
 Type: enum_or_text
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
+Allowed (warning (free text allowed)): endurance | resistance | interval_or_sprint | mixed_or_concurrent | intermittent_team_or_racket_sport | other | NR | NA | UNCLEAR
 Source: legacy_61_fields["exercise_mode"] (exposure)</t>
       </text>
     </comment>
@@ -788,13 +796,13 @@
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
-Allowed (strict): pre_exercise_baseline | during_exercise | immediate_post | recovery_post | nonexercise_control | matched_control | other | NR | NA | UNCLEAR
+Allowed (strict): pre_exercise_baseline | during_exercise | immediate_post | recovery_post | nonexercise_control | matched_control | periodic_training_monitoring | resting_habitual_group | other | NR | NA | UNCLEAR
 Source: controlled_vocabulary.sample_role</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>保留原始运动前/中/后时间，不能只留分箱
+        <t>保留原始运动前/中/后时间，不能只留分箱 v3.1: value = earliest stated bound; unit min/h/d (controlled_vocabulary.time_unit); see time_bin_rules.boundary_rules.
 Type: object
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -803,7 +811,7 @@
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>保留原始运动前/中/后时间，不能只留分箱
+        <t>保留原始运动前/中/后时间，不能只留分箱 v3.1: value = earliest stated bound; unit min/h/d (controlled_vocabulary.time_unit); see time_bin_rules.boundary_rules.
 Type: object
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -812,10 +820,11 @@
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>保留原始运动前/中/后时间，不能只留分箱
+        <t>保留原始运动前/中/后时间，不能只留分箱 v3.1: value = earliest stated bound; unit min/h/d (controlled_vocabulary.time_unit); see time_bin_rules.boundary_rules.
 Type: object
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
+Allowed (warning (free text allowed)): min | h | d | NR | NA | UNCLEAR
 Source: legacy_61_fields["exact_times"] (sampling)</t>
       </text>
     </comment>
@@ -831,16 +840,17 @@
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t>全血/血浆/血清/PBMC/唾液/尿/汗/组织分别编码
+        <t>全血/血浆/血清/PBMC/唾液/尿/汗/组织分别编码 v3.1: controlled_vocabulary.matrix.
 Type: enum_or_text
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
+Allowed (warning (free text allowed)): whole_blood | PBMC | sorted_or_isolated_immune_cells | plasma | serum | saliva | urine | sweat | extracellular_vesicles | other_cell_free_biofluid | tissue | other | NR | NA | UNCLEAR
 Source: legacy_61_fields["matrix"] (sampling)</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
-        <t>Assay/platform of this sample set (e.g. flow-cytometry panel, ELISA kit, Olink panel, RNA-seq); rows are split when n differs between platforms. Sample-set counterpart of measurements.platform.
+        <t>Assay platform(s) applied to this sample set ("; "-separated, e.g. "flow cytometry; Olink Target 96 Inflammation"); the row is split by platform only when the report gives a platform-specific n that differs. Sample-set counterpart of measurements.platform.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -849,7 +859,7 @@
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>每组、每平台、每时间点实际人数
+        <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).
 Type: separate_counts
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
@@ -858,7 +868,7 @@
     </comment>
     <comment ref="U1" authorId="0" shapeId="0">
       <text>
-        <t>每组、每平台、每时间点实际人数
+        <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).
 Type: separate_counts
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
@@ -867,7 +877,7 @@
     </comment>
     <comment ref="V1" authorId="0" shapeId="0">
       <text>
-        <t>每组、每平台、每时间点实际人数
+        <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).
 Type: separate_counts
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
@@ -876,7 +886,7 @@
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
       <text>
-        <t>每组、每平台、每时间点实际人数
+        <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).
 Type: separate_counts
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: General + integer/missing-code validation
@@ -976,7 +986,7 @@
     </comment>
     <comment ref="AH1" authorId="0" shapeId="0">
       <text>
-        <t>Free-text notes on the sample set (timing-anchor ambiguity, pooling, exclusions) with locators.
+        <t>Free-text notes on the sample set (timing-anchor ambiguity, pooling, exclusions; flags TIME_BIN_STRADDLE, DAY_LEVEL_TIMING, IMMEDIATE_NONNUMERIC, DERIVED_N) with locators.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1022,7 +1032,7 @@
     </comment>
     <comment ref="AM1" authorId="0" shapeId="0">
       <text>
-        <t>Basis used to identify/count biological donors and relation to participant IDs.
+        <t>Basis used to identify/count biological donors; only for single-cell, single-nucleus or sorted-cell assays, NA otherwise (values defined in analysis_unit_rules.single_cell).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1079,7 +1089,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Primary key of measurements (One assay-level tested-universe summary OR one named candidate/feature × comparison; include all named immune candidates from original aims/methods regardless of significance.).
+        <t>Primary key of measurements (Conventional/targeted assays: one named analyte × one author-reported statistical test (one row for a time main effect across time points; one row per time-point contrast only when each contrast is the reported test). Omics: one assay_universe_summary row per analysis universe (platform × matrix × analysis route) plus one named_immune_candidate row per candidate named in the main text, main tables or figure legends; supplementary result tables are summarised in the universe row by counts and locators; candidates prespecified in the original aims/methods are always enumerated (including nulls); set-level results (pathways, modules, hit counts) as one reported_result_summary row per analysis.).
 Type: identifier
 Missing values: forbidden (identifier)
 Excel format: Text (@)
@@ -1336,7 +1346,7 @@
     </comment>
     <comment ref="AC1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish assay-level universe summary from named candidate and reported-result rows; connect rows from one assay universe.
+        <t>record_type (assay_universe_summary / named_immune_candidate / reported_result_summary; definitions in controlled_vocabulary_definitions.measurement_record_type) and assay_universe_id linking named and summary rows to their universe row.
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1346,7 +1356,7 @@
     </comment>
     <comment ref="AD1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish assay-level universe summary from named candidate and reported-result rows; connect rows from one assay universe.
+        <t>record_type (assay_universe_summary / named_immune_candidate / reported_result_summary; definitions in controlled_vocabulary_definitions.measurement_record_type) and assay_universe_id linking named and summary rows to their universe row.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1419,27 +1429,27 @@
     </comment>
     <comment ref="AL1" authorId="0" shapeId="0">
       <text>
-        <t>Record candidate selection rule, source in original aims/methods/protocol, and timing. Original aims/methods qualify without preregistration.
+        <t>Candidate selection rule, basis and prespecification timing; apply to every non-universe row including conventional targeted assays; prespecification refers to the named candidate, not the platform (controlled_vocabulary_definitions.candidate_fields).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
-Allowed (strict): all_named_immune_candidates_from_original_aims_methods_regardless_of_significance | complete_targeted_panel | author_reported_feature_set | other_source_defined_rule | NR | NA | UNCLEAR
+Allowed (strict): all_named_immune_candidates_from_original_aims_methods_regardless_of_significance | complete_targeted_panel | author_reported_feature_set | statistically_selected_hits_from_untargeted_screen | other_source_defined_rule | NR | NA | UNCLEAR
 Source: new_operational_fields_not_in_legacy_61["measurements.candidate_selection_rule / basis / prespecification_status"]</t>
       </text>
     </comment>
     <comment ref="AM1" authorId="0" shapeId="0">
       <text>
-        <t>Record candidate selection rule, source in original aims/methods/protocol, and timing. Original aims/methods qualify without preregistration.
+        <t>Candidate selection rule, basis and prespecification timing; apply to every non-universe row including conventional targeted assays; prespecification refers to the named candidate, not the platform (controlled_vocabulary_definitions.candidate_fields).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
-Allowed (strict): original_aims | original_methods | registered_protocol_or_analysis_plan | supplement | other | NR | NA | UNCLEAR
+Allowed (strict): original_aims | original_methods | registered_protocol_or_analysis_plan | supplement | results_statistical_selection | other | NR | NA | UNCLEAR
 Source: new_operational_fields_not_in_legacy_61["measurements.candidate_selection_rule / basis / prespecification_status"]</t>
       </text>
     </comment>
     <comment ref="AN1" authorId="0" shapeId="0">
       <text>
-        <t>Record candidate selection rule, source in original aims/methods/protocol, and timing. Original aims/methods qualify without preregistration.
+        <t>Candidate selection rule, basis and prespecification timing; apply to every non-universe row including conventional targeted assays; prespecification refers to the named candidate, not the platform (controlled_vocabulary_definitions.candidate_fields).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1488,7 +1498,7 @@
     </comment>
     <comment ref="AS1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish explicit null/nonsignificant result from a named candidate whose result was not retrievable or not separately reported.
+        <t>Distinguish explicit null/nonsignificant result from a named candidate whose result was not retrievable or not separately reported; follows the author-reported test and stated threshold (controlled_vocabulary_definitions.result_status).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1498,7 +1508,7 @@
     </comment>
     <comment ref="AT1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1508,7 +1518,7 @@
     </comment>
     <comment ref="AU1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1517,7 +1527,7 @@
     </comment>
     <comment ref="AV1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1526,7 +1536,7 @@
     </comment>
     <comment ref="AW1" authorId="0" shapeId="0">
       <text>
-        <t>Figure and panel from which a value was read (e.g. "Fig. 3B, left"); required when effect_value_source = digitized_from_figure, otherwise NA.
+        <t>Figure and panel showing the result (e.g. "Fig. 3B, left"); filled whenever the result is shown only in a figure (FIGURE_ONLY) and whenever a value is digitized; otherwise NA.
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1535,7 +1545,7 @@
     </comment>
     <comment ref="AX1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1544,7 +1554,7 @@
     </comment>
     <comment ref="AY1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1553,7 +1563,7 @@
     </comment>
     <comment ref="AZ1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1562,7 +1572,7 @@
     </comment>
     <comment ref="BA1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1571,7 +1581,7 @@
     </comment>
     <comment ref="BB1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1580,7 +1590,7 @@
     </comment>
     <comment ref="BC1" authorId="0" shapeId="0">
       <text>
-        <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.
+        <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).
 Type: string
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1589,17 +1599,17 @@
     </comment>
     <comment ref="BD1" authorId="0" shapeId="0">
       <text>
-        <t>Marker family (controlled_vocabulary.marker_family; conventional vs omics classes in vocabulary_crosswalks.marker_family_classes) used to organise Figure 1 and the per-marker validation-readiness map (Figure 2). Assigned per row from the measured analyte/platform, not from author framing.
+        <t>Marker family (controlled_vocabulary.marker_family; conventional vs omics classes in vocabulary_crosswalks.marker_family_classes) used to organise Figure 1 and the per-marker validation-readiness map (Figure 2). Named analytes that map to a conventional family are classified by analyte whatever the platform; omics families for universe/summary rows and features without a conventional family (controlled_vocabulary_definitions.marker_family).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
-Allowed (strict): leukocyte_redistribution | NK_count_or_cytotoxicity | neutrophil_function | T_cell_subsets_or_function | mucosal_sIgA | cytokine_or_inflammatory_mediator | immunoglobulin_or_complement | immune_cell_transcriptome | proteome | metabolome_or_lipidome | epigenome | ncRNA | single_cell | other | NR | NA | UNCLEAR
+Allowed (strict): leukocyte_redistribution | NK_count_or_cytotoxicity | neutrophil_function | T_cell_subsets_or_function | mucosal_sIgA | mucosal_antimicrobial_protein | cytokine_or_inflammatory_mediator | immunoglobulin_or_complement | immune_cell_transcriptome | proteome | metabolome_or_lipidome | epigenome | ncRNA | single_cell | other | NR | NA | UNCLEAR
 Source: new_operational_fields_not_in_legacy_61["measurements.marker_family"]</t>
       </text>
     </comment>
     <comment ref="BE1" authorId="0" shapeId="0">
       <text>
-        <t>Status of the second-reviewer check of a digitized value (controlled_vocabulary.digitization_check); NA when effect_value_source is not digitized_from_figure.
+        <t>Status of the second-reviewer check of a digitized value (controlled_vocabulary.digitization_check); NA when effect_value_source is not digitized_from_figure (always NA in v3.1: figure values are not digitised).
 Type: enum
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
@@ -1619,7 +1629,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Primary key of precision_validation (one report/cohort/measurement × one domain).
+        <t>Primary key of precision_validation (one report × cohort × marker_family × one domain (default: one set of seven domain rows per report × cohort × marker family, measurement_id null); an additional analyte-level row (measurement_id = one measurement ID) only for a domain where the report gives analyte-specific evidence. No rows for background reports.).
 Type: identifier
 Missing values: forbidden (identifier)
 Excel format: Text (@)
@@ -1841,6 +1851,16 @@
 Excel format: Text (@)
 Allowed (strict): none | resampling_same_participants | participant_level_holdout_same_cohort | independent_site_or_cohort | NR | NA | UNCLEAR
 Source: new_operational_fields_not_in_legacy_61["precision_validation.validation_split"]</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Marker family (controlled_vocabulary.marker_family) of the domain-row set: one set of seven domain rows per report × cohort × marker family; optional (v3.1, PRE-004), appended as the last column; null on rows created before v3.1.
+Type: enum
+Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
+Excel format: Text (@)
+Allowed (strict): leukocyte_redistribution | NK_count_or_cytotoxicity | neutrophil_function | T_cell_subsets_or_function | mucosal_sIgA | mucosal_antimicrobial_protein | cytokine_or_inflammatory_mediator | immunoglobulin_or_complement | immune_cell_transcriptome | proteome | metabolome_or_lipidome | epigenome | ncRNA | single_cell | other | NR | NA | UNCLEAR
+Source: new_operational_fields_not_in_legacy_61["precision_validation.marker_family"]</t>
       </text>
     </comment>
   </commentList>
@@ -2018,10 +2038,11 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>随机/交叉/单组前后/前瞻队列/横断面
+        <t>随机/交叉/单组前后/前瞻队列/横断面 v3.1: controlled_vocabulary.design.
 Type: enum_or_text
 Missing values: NR/NA/UNCLEAR after source review; blank = not yet extracted
 Excel format: Text (@)
+Allowed (warning (free text allowed)): randomized_parallel | randomized_crossover | nonrandomized_controlled | nonrandomized_crossover | single_group_pre_post | prospective_cohort | cross_sectional | case_series_or_case_report | other | NR | NA | UNCLEAR
 Source: legacy_61_fields["design"] (exposure)</t>
       </text>
     </comment>
@@ -2104,142 +2125,172 @@
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
+        <t>Source: training_status; mode: warning (free text allowed)</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
         <t>Source: adult_stratum_separable; mode: strict</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>Source: older_adult_subgroup; mode: strict</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Source: scope_stream; mode: warning (multi-valued, "; ")</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Source: exercise_mode; mode: warning (free text allowed)</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>Source: sample_role; mode: strict</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Source: time_unit; mode: warning (free text allowed)</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <t>Source: time_bin; mode: strict</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
+      <text>
+        <t>Source: matrix; mode: warning (free text allowed)</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>Source: participant_linkage; mode: strict</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>Source: donor_count_basis; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>Source: within_organising_window; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>Source: biological_level; mode: warning (free text allowed)</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AM1" authorId="0" shapeId="0">
       <text>
         <t>Source: omics_integration; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AO1" authorId="0" shapeId="0">
       <text>
         <t>Source: result_direction; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
         <t>Source: measurement_record_type; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AK1" authorId="0" shapeId="0">
+    <comment ref="AS1" authorId="0" shapeId="0">
       <text>
         <t>Source: candidate_selection_rule; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AM1" authorId="0" shapeId="0">
+    <comment ref="AU1" authorId="0" shapeId="0">
       <text>
         <t>Source: candidate_selection_basis; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0">
+    <comment ref="AW1" authorId="0" shapeId="0">
       <text>
         <t>Source: candidate_prespecification_status; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AQ1" authorId="0" shapeId="0">
+    <comment ref="AY1" authorId="0" shapeId="0">
       <text>
         <t>Source: supplement_availability; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AS1" authorId="0" shapeId="0">
+    <comment ref="BA1" authorId="0" shapeId="0">
       <text>
         <t>Source: candidate_result_status; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AU1" authorId="0" shapeId="0">
+    <comment ref="BC1" authorId="0" shapeId="0">
       <text>
         <t>Source: effect_value_source; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AW1" authorId="0" shapeId="0">
+    <comment ref="BE1" authorId="0" shapeId="0">
       <text>
         <t>Source: marker_family; mode: strict</t>
       </text>
     </comment>
-    <comment ref="AY1" authorId="0" shapeId="0">
+    <comment ref="BG1" authorId="0" shapeId="0">
       <text>
         <t>Source: digitization_check; mode: strict</t>
       </text>
     </comment>
-    <comment ref="BA1" authorId="0" shapeId="0">
+    <comment ref="BI1" authorId="0" shapeId="0">
       <text>
         <t>Source: precision_domain; mode: strict</t>
       </text>
     </comment>
-    <comment ref="BC1" authorId="0" shapeId="0">
+    <comment ref="BK1" authorId="0" shapeId="0">
       <text>
         <t>Source: evidence_state; mode: strict</t>
       </text>
     </comment>
-    <comment ref="BE1" authorId="0" shapeId="0">
+    <comment ref="BM1" authorId="0" shapeId="0">
       <text>
         <t>Source: relationship_tags; mode: warning (multi-valued, "; ")</t>
       </text>
     </comment>
-    <comment ref="BG1" authorId="0" shapeId="0">
+    <comment ref="BO1" authorId="0" shapeId="0">
       <text>
         <t>Source: clinical_endpoint; mode: warning (free text allowed)</t>
       </text>
     </comment>
-    <comment ref="BI1" authorId="0" shapeId="0">
+    <comment ref="BQ1" authorId="0" shapeId="0">
       <text>
         <t>Source: intended_use; mode: strict</t>
       </text>
     </comment>
-    <comment ref="BK1" authorId="0" shapeId="0">
+    <comment ref="BS1" authorId="0" shapeId="0">
       <text>
         <t>Source: linkage_subtype; mode: strict</t>
       </text>
     </comment>
-    <comment ref="BM1" authorId="0" shapeId="0">
+    <comment ref="BU1" authorId="0" shapeId="0">
       <text>
         <t>Source: validation_use_subtype; mode: strict</t>
       </text>
     </comment>
-    <comment ref="BO1" authorId="0" shapeId="0">
+    <comment ref="BW1" authorId="0" shapeId="0">
       <text>
         <t>Source: validation_split; mode: strict</t>
+      </text>
+    </comment>
+    <comment ref="BY1" authorId="0" shapeId="0">
+      <text>
+        <t>Source: marker_family; mode: strict</t>
+      </text>
+    </comment>
+    <comment ref="CA1" authorId="0" shapeId="0">
+      <text>
+        <t>Source: design; mode: warning (free text allowed)</t>
       </text>
     </comment>
   </commentList>
@@ -2536,7 +2587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2578,7 +2629,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2641,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>scripts/build_workbooks.py v1.1.0</t>
+          <t>scripts/build_workbooks.py v1.3.0</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2665,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>empty template; no included studies or extraction records</t>
+          <t>empty template; no included studies or extraction records (v3.1, amendment PRE-004)</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2697,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>metadata.version=3.0; metadata.date=2026-10-04; metadata.schema_verified_date=2026-10-04; sha256=c1f78637319a6cae…</t>
+          <t>metadata.version=3.1; metadata.date=2026-10-05; metadata.schema_verified_date=2026-10-05; sha256=a0a2c76106353716…</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2709,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>metadata.schema_version=3.0; metadata.created_date=2026-10-02; sha256=3dd34471d04aa0a6…</t>
+          <t>metadata.schema_version=3.1; metadata.created_date=2026-10-02; sha256=4bd52fb74ffc7d53…</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2721,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>3.0; sha256=59bdf7c855de5a79…</t>
+          <t>3.1; sha256=eed2491e6aa32f62…</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2733,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>protocol_version=3.0; protocol_date=2026-10-04; template_status=blank_template_no_formal_screening_results; sha256=0ae524e6b536bd6a…</t>
+          <t>protocol_version=3.1; protocol_date=2026-10-05; template_status=blank_template_no_formal_screening_results; sha256=f79df1b2bf730547…</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2745,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>protocol_version=3.0; protocol_date=2026-10-04; taxonomy_status=predefined_fixed_hierarchy_no_formal_exclusion_results; sha256=9515e0b749770aec…</t>
+          <t>protocol_version=3.1; protocol_date=2026-10-05; taxonomy_status=predefined_fixed_hierarchy_no_formal_exclusion_results; sha256=9610d43070d561f2…</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2829,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>row unit: one report/version/correction | PK: report_id | FK: — | 24 columns | 一篇出版报告或可区分版本；与cohort经桥表关联。</t>
+          <t>row unit: one report or distinguishable version (preprint, accepted manuscript, version of record, correction): one reports row per version. Version rows of one report share the stem of reference_id with a suffix (e.g. R01, R01-V1) and, once the version relationship is verified, are linked through report_cohort_links to the same study_id (study family) and cohort_id; a version stub carries bibliographic and version fields only. | PK: report_id | FK: — | 24 columns | 一篇出版报告或可区分版本；与cohort经桥表关联。</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2865,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>row unit: one group × assay/matrix × exact timepoint sample set | PK: sample_set_id | FK: report_id -&gt; reports.report_id; study_id -&gt; study_families.study_id; cohort_id -&gt; cohorts.cohort_id | 43 columns | 同一报告/队列/组别 × 矩阵 × assay/platform × 精确采样时间的样本集合；分母不同时拆行。</t>
+          <t>row unit: one cohort × group/arm × matrix × time point as sampled in the Methods (whether or not a result is reported for that combination); assay platforms are listed in assay_platform ("; "-separated). Split by platform only when the report gives a platform-specific n that differs between platforms at that time point; split by analysis subgroup only when subgroup n and subgroup results are reported; control-arm time points get their own rows. | PK: sample_set_id | FK: report_id -&gt; reports.report_id; study_id -&gt; study_families.study_id; cohort_id -&gt; cohorts.cohort_id | 43 columns | 同一报告/队列/组别 × 基质 × 实际采样时点的样本集合；平台写入 assay_platform（多值）；仅当原文给出不同的平台 n 时按平台拆行。</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2877,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>row unit: One assay-level tested-universe summary OR one named candidate/feature × comparison; include all named immune candidates from original aims/methods regardless of significance. | PK: measurement_id | FK: report_id -&gt; reports.report_id; study_id -&gt; study_families.study_id; cohort_id -&gt; cohorts.cohort_id; sample_set_ids[] -&gt; sample_sets.sample_set_id | 57 columns | 已报告分析物/明确特征集 × 统计比较；只记录原文结果。</t>
+          <t>row unit: Conventional/targeted assays: one named analyte × one author-reported statistical test (one row for a time main effect across time points; one row per time-point contrast only when each contrast is the reported test). Omics: one assay_universe_summary row per analysis universe (platform × matrix × analysis route) plus one named_immune_candidate row per candidate named in the main text, main tables or figure legends; supplementary result tables are summarised in the universe row by counts and locators; candidates prespecified in the original aims/methods are always enumerated (including nulls); set-level results (pathways, modules, hit counts) as one reported_result_summary row per analysis. | PK: measurement_id | FK: report_id -&gt; reports.report_id; study_id -&gt; study_families.study_id; cohort_id -&gt; cohorts.cohort_id; sample_set_ids[] -&gt; sample_sets.sample_set_id | 57 columns | 已报告分析物 × 作者报告的统计检验，或组学检测全集汇总行、具名候选行与集合层面结果行；只记录原文结果。</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2889,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>row unit: one report/cohort/measurement × one domain | PK: precision_record_id | FK: report_id -&gt; reports.report_id; study_id -&gt; study_families.study_id; cohort_id -&gt; cohorts.cohort_id; measurement_id -&gt; measurements.measurement_id (optional) | 24 columns | 多维precision/validation长表；每行仅一个维度，不汇总成总分；evidence_state 为逐标志物 validation-readiness map 的单元格状态（见 metadata.validation_readiness_map_definition）。</t>
+          <t>row unit: one report × cohort × marker_family × one domain (default: one set of seven domain rows per report × cohort × marker family, measurement_id null); an additional analyte-level row (measurement_id = one measurement ID) only for a domain where the report gives analyte-specific evidence. No rows for background reports. | PK: precision_record_id | FK: report_id -&gt; reports.report_id; study_id -&gt; study_families.study_id; cohort_id -&gt; cohorts.cohort_id; measurement_id -&gt; measurements.measurement_id (optional) | 25 columns | 多维precision/validation长表；默认每个 报告 × 队列 × 标志物族 建一组七个域行，仅在原文有分析物特异证据时另建分析物级行；每行仅一个维度，不汇总成总分；evidence_state 为逐标志物 validation-readiness map 的单元格状态（见 metadata.validation_readiness_map_definition）。</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2942,7 @@
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>A sample_set is one group × matrix × assay/platform × exact time. Split when n or measurement process differs.</t>
+          <t>A sample_set is one cohort × group/arm × matrix × time point as sampled; platforms are listed in assay_platform. Split by platform only when a platform-specific n is reported and differs; split by analysis subgroup only when subgroup n and results are reported; each control-arm time point is its own row (PRE-004).</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2956,7 @@
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>For assays with large feature spaces, record tested universe and source/availability; enumerate all named immune candidates identified in original aims/methods in accessible article text and supplements without a significance filter. Do not fabricate rows for unnamed/unreported features.</t>
+          <t>For assays with large feature spaces, record the tested universe and source/availability in an assay_universe_summary row; enumerate every immune candidate named in the main text, main tables or figure legends, and every candidate prespecified in the original aims/methods wherever its result appears, without a significance filter. Features that appear only in supplementary result tables are summarised in the universe row (counts and locators), not enumerated. Do not fabricate rows for unnamed/unreported features (PRE-004).</t>
         </is>
       </c>
     </row>
@@ -2972,266 +3023,329 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Row IDs are mandatory patterns numbered in order of appearance in the report: measurements M-&lt;ref&gt;-NNN, sample_sets SS-&lt;ref&gt;-NN, precision_validation PV-&lt;ref&gt;-NNN (three/two digits, zero-padded; &lt;ref&gt; = reports.reference_id, e.g. R59); cohort, study and link IDs follow C-&lt;ref&gt;-NN, S-&lt;ref&gt;-NN and L-&lt;ref&gt;-NN. No custom prefixes or analyte codes inside IDs (PRE-004).</t>
+        </is>
+      </c>
+    </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>完整性检查 Referential integrity checks (extraction_template.json)</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>precision_validation: default one set of seven domain rows per report × cohort × marker_family (precision_validation.marker_family); analyte-level rows only where analyte-specific domain evidence exists; measurement_id is one measurement ID or null, never a list or the string "NA" (PRE-004).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>all foreign keys resolve</t>
+          <t>Background reports (scope_stream = background; screening disposition RETAIN_BACKGROUND) are charted at reduced depth: bibliographic, design, population, assay platforms and n only (reports, study_families, cohorts, report_cohort_links, extraction_provenance; sample_sets one row per cohort × group × matrix with time_bin NA; measurements assay_universe_summary rows describing platforms only, result fields NA); no named-candidate or per-marker result rows and no precision_validation rows; one extractor plus one checker (PRE-004).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>cohort.study_id agrees with bridge/sample/measurement study_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>each measurement.sample_set_ids[] resolves to sample_sets in the same cohort/study</t>
+          <t>Screening and consensus fields in charting workbooks (reports.screening_decision_reviewer_A/B, consensus_screening_decision, primary_fulltext_exclusion_reason) are copied verbatim from the locked screening workbook / merge output and stay null when no screening record exists; extractors and AI tools never enter eligibility opinions in them (PRE-004).</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>each precision row resolves to a report and any optional measurement</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>完整性检查 Referential integrity checks (extraction_template.json)</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Each assay_universe_id links one assay-level summary to its named candidates/result rows; preserve tested-universe and supplement locators.</t>
+          <t>all foreign keys resolve</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Primary keys are unique, nonempty stable IDs; required linkage keys are never NR/NA/UNCLEAR.</t>
+          <t>cohort.study_id agrees with bridge/sample/measurement study_id</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Every sample, measurement and precision report_id/study_id/cohort_id tuple exists in report_cohort_links.</t>
+          <t>each measurement.sample_set_ids[] resolves to sample_sets in the same cohort/study</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Each measurement.sample_set_ids[] belongs to its report as well as its cohort/study; optional precision measurement_id, when present, matches the same report/study/cohort.</t>
+          <t>each precision row resolves to a report and any optional measurement</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Cohort-specific A/B membership uses report_cohort_links.scope_streams; one cohort in both streams is counted once overall.</t>
+          <t>Each assay_universe_id links one assay-level summary to its named candidates/result rows; preserve tested-universe and supplement locators.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>sample_sets.within_organising_window agrees with time_bin through time_bin_window_position.</t>
+          <t>Primary keys are unique, nonempty stable IDs; required linkage keys are never NR/NA/UNCLEAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Every sample, measurement and precision report_id/study_id/cohort_id tuple exists in report_cohort_links.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>护栏 Guardrails</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n"/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Each measurement.sample_set_ids[] belongs to its report as well as its cohort/study; optional precision measurement_id, when present, matches the same report/study/cohort.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>No decisions or extracted scientific values are prefilled.</t>
+          <t>Cohort-specific A/B membership uses report_cohort_links.scope_streams; one cohort in both streams is counted once overall.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>No aggregate precision score, readiness score or ranking; domain rows feed only the validation-readiness map (see the validation-readiness map definition in this file; contract 8.3e).</t>
+          <t>sample_sets.within_organising_window agrees with time_bin through time_bin_window_position.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Participant n, biological samples, cells and technical replicates remain separate.</t>
+          <t>Row IDs follow M-&lt;ref&gt;-NNN, SS-&lt;ref&gt;-NN and PV-&lt;ref&gt;-NNN in order of appearance; no custom prefixes.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Named immune candidates found in original aims/methods and accessible supplements are recorded regardless of significance; unreported feature rows are not invented.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Values read from figures must be predeclared as a separate digitization procedure, tagged digitized_from_figure, and checked by two reviewers.</t>
+          <t>precision_validation.measurement_id is a single measurement ID or null; precision_validation.marker_family, when filled, matches the marker_family of the measurements it summarises.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Support B (retained; cross-bout open-window monitoring layer) requires same marker + same participants across &gt;=2 distinct bout_id values, known timing and baseline/comparator; deduplicated against Core A by cohort_id.</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>护栏 Guardrails</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n"/>
     </row>
     <row r="73">
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Samples later than 72 h after cessation are extracted and tagged outside_window_recovery; nothing is excluded for falling outside the 0-72 h organising window.</t>
+          <t>No decisions or extracted scientific values are prefilled.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Exercise duration and intensity are recorded as reported and never used as eligibility thresholds.</t>
+          <t>No aggregate precision score, readiness score or ranking; domain rows feed only the validation-readiness map (see the validation-readiness map definition in this file; contract 8.3e).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Only adults (&gt;= 18 y) or separable adult strata are charted; older adults are flagged as a subgroup.</t>
+          <t>Participant n, biological samples, cells and technical replicates remain separate.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Author open-window interpretation is a descriptive tag; it never affects eligibility or weighting.</t>
+          <t>Immune candidates named in the main text, main tables or figure legends, and candidates prespecified in the original aims/methods, are recorded regardless of significance; supplementary result tables are summarised by counts and locators in the assay-universe row; unreported feature rows are not invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Figure-only values are not digitised: record direction and significance only, effect_value NR, figure_panel_locator filled, flag FIGURE_ONLY (PRE-004).</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>维护规则 Maintenance rule</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n"/>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Support B (retained; cross-bout open-window monitoring layer) requires same marker + same participants across &gt;=2 distinct bout_id values, known timing and baseline/comparator; deduplicated against Core A by cohort_id.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>先修改 JSON 模板，再运行脚本重新生成；不得手工修改生成的 xlsx 结构。工作表保护无密码，仅防误改结构；行可插入/删除，可筛选排序。</t>
+          <t>Samples later than 72 h after cessation are extracted and tagged outside_window_recovery; nothing is excluded for falling outside the 0-72 h organising window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Exercise duration and intensity are recorded as reported and never used as eligibility thresholds.</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>模板解释 Interpretations of JSON fields</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n"/>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Only adults (&gt;= 18 y) or separable adult strata are charted; older adults are flagged as a subgroup.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Nested JSON objects (analyte_id, extractor_a_b, ai_assistance) are flattened to "parent.child" columns.</t>
+          <t>Author open-window interpretation is a descriptive tag; it never affects eligibility or weighting.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>JSON arrays (source_locator, immune_link, scope_streams, sample_set_ids, relationship_tags, registry_ids, ...) are stored in one cell with values separated by "; "; their dropdowns use a warning (not stop) so several values can be entered.</t>
+          <t>Background reports are charted at reduced depth (bibliographic, design, population, platforms, n), with no per-marker results and no precision_validation rows; one extractor plus one checker.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Vocabulary-to-column mapping is by identical name, plus three aliases: report_cohort_links.scope_streams &lt;- scope_stream, measurements.record_type &lt;- measurement_record_type, measurements.result_status &lt;- candidate_result_status.</t>
+          <t>Screening and consensus fields are copied from the locked screening records only; no eligibility opinion is written into them.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>reports.primary_fulltext_exclusion_reason &lt;- fulltext_exclusion_codes.json hierarchy and reports.consensus_screening_decision &lt;- screening_dispositions (cross-file; warning style).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>NR/NA/UNCLEAR are appended to a dropdown when the field is a legacy field whose missing_value_rule allows them, or the vocabulary already contains them; they are not appended to structural lists (precision_domain, record_type, scope_streams). Primary/foreign-key columns reject NR/NA/UNCLEAR (missing_value_semantics.identifiers).</t>
+          <t>Count fields hold integers or bare missing codes; explanations go to notes.</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Fields with legacy data_type enum (or new fields with a vocabulary) get a strict dropdown; enum_or_text / string_or_object fields with a vocabulary get a warning dropdown that still allows free text.</t>
-        </is>
-      </c>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>维护规则 Maintenance rule</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n"/>
     </row>
     <row r="88">
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Count columns (legacy integer_or_missing_code / separate_counts, plus new fields named n_*, *_count, *_n) accept a non-negative integer or NR/NA/UNCLEAR. Every other column is Text format (@) to stop Excel auto-conversion of IDs, DOIs, PMIDs, gene names (SEPT7, MARCH1), ratios (1-2) and leading zeros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Header comments: definition from legacy_61_fields (exact table.column, or a same-named legacy field in another table, marked as such), new_operational_fields_not_in_legacy_61 (slash shorthand expanded), primary/foreign-key specs, or the controlled-vocabulary name; columns with none of these are marked "no definition in data_dictionary.json".</t>
-        </is>
-      </c>
+          <t>先修改 JSON 模板，再运行脚本重新生成；不得手工修改生成的 xlsx 结构。工作表保护无密码，仅防误改结构；行可插入/删除，可筛选排序。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>模板解释 Interpretations of JSON fields</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>无定义字段 Columns without a dictionary definition</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n"/>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Nested JSON objects (analyte_id, extractor_a_b, ai_assistance) are flattened to "parent.child" columns.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>JSON arrays (source_locator, immune_link, scope_streams, sample_set_ids, relationship_tags, registry_ids, ...) are stored in one cell with values separated by "; "; their dropdowns use a warning (not stop) so several values can be entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Vocabulary-to-column mapping is by identical name, plus three aliases: report_cohort_links.scope_streams &lt;- scope_stream, measurements.record_type &lt;- measurement_record_type, measurements.result_status &lt;- candidate_result_status.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>模板不一致提示 Template issues detected</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="n"/>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>reports.primary_fulltext_exclusion_reason &lt;- fulltext_exclusion_codes.json hierarchy and reports.consensus_screening_decision &lt;- screening_dispositions (cross-file; warning style).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>NR/NA/UNCLEAR are appended to a dropdown when the field is a legacy field whose missing_value_rule allows them, or the vocabulary already contains them; they are not appended to structural lists (precision_domain, record_type, scope_streams). Primary/foreign-key columns reject NR/NA/UNCLEAR (missing_value_semantics.identifiers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Fields with legacy data_type enum (or new fields with a vocabulary) get a strict dropdown; enum_or_text / string_or_object fields with a vocabulary get a warning dropdown that still allows free text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Count columns (legacy integer_or_missing_code / separate_counts, plus new fields named n_*, *_count, *_n) accept a non-negative integer or NR/NA/UNCLEAR. Every other column is Text format (@) to stop Excel auto-conversion of IDs, DOIs, PMIDs, gene names (SEPT7, MARCH1), ratios (1-2) and leading zeros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Header comments: definition from legacy_61_fields (exact table.column, or a same-named legacy field in another table, marked as such), new_operational_fields_not_in_legacy_61 (slash shorthand expanded), primary/foreign-key specs, or the controlled-vocabulary name; columns with none of these are marked "no definition in data_dictionary.json".</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>无定义字段 Columns without a dictionary definition</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>模板不一致提示 Template issues detected</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>none detected by the generator</t>
         </is>
@@ -3249,7 +3363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O191"/>
+  <dimension ref="A1:O192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3452,7 +3566,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Project reference identifier: the record_id of the retained deduplicated screening record, or for pilot items the restart ledger ID (e.g. R59). Text; never reused.</t>
+          <t>Project reference identifier: the record_id of the retained deduplicated screening record, or for pilot items the restart ledger ID (e.g. R59). Version rows of the same report add a suffix (R01-V1, R01-V2). Text; never reused.</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -3841,7 +3955,7 @@
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>同行评审/预印本/会议摘要/更正/撤稿</t>
+          <t>同行评审/预印本/会议摘要/更正/撤稿 v3.1: peer-review/version status only; short-format article type goes to version_label (controlled_vocabulary_definitions.publication_status).</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -3904,7 +4018,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>在线首发与当前版本日期</t>
+          <t>在线首发与当前版本日期 v3.1: ISO 8601 (YYYY-MM-DD) online publication date of the version consulted; else issue date; else accepted date with flag ACCEPTED_DATE_USED in reviewer_notes.</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -3967,7 +4081,7 @@
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Version label as published (e.g. version of record, online first, bioRxiv v2, correction notice); paired with version_date.</t>
+          <t>Version label and article type as published (e.g. "version of record; short communication", "bioRxiv v2", "Did You Know? (peer reviewed)", correction notice); paired with version_date.</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -4349,7 +4463,7 @@
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Full-text screening disposition of human Reviewer A, copied verbatim from Reviewer A's locked screening workbook / merge output (04_screening/screening_log_template.json field_schema.screening_dispositions, FT stage). A reviewer decision, not Core A membership. Renamed in v3 from screening_A (not legacy-61).</t>
+          <t>Full-text screening disposition of human Reviewer A, copied verbatim from Reviewer A's locked screening workbook / merge output (04_screening/screening_log_template.json field_schema.screening_dispositions, FT stage). A reviewer decision, not Core A membership. Renamed in v3 from screening_A (not legacy-61). Copy-only; null when no screening record exists.</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -4400,7 +4514,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Full-text screening disposition of human Reviewer B, copied verbatim from Reviewer B's locked screening workbook / merge output (screening_dispositions, FT stage). A reviewer decision, not Support B membership. Renamed in v3 from screening_B (not legacy-61).</t>
+          <t>Full-text screening disposition of human Reviewer B, copied verbatim from Reviewer B's locked screening workbook / merge output (screening_dispositions, FT stage). A reviewer decision, not Support B membership. Renamed in v3 from screening_B (not legacy-61). Copy-only; null when no screening record exists.</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -4433,7 +4547,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ADVANCE | EXCLUDE_TA | FRONTIER_PREPRINT | AWAITING_CLASSIFICATION | INCLUDE_A | INCLUDE_B | INCLUDE_A_AND_B | EXCLUDE_FT | NOT_RETRIEVED | AWAITING_TRANSLATION | DUPLICATE_RECORD | DUPLICATE_VERSION | NR | NA | UNCLEAR</t>
+          <t>ADVANCE_TO_ABSTRACT | EXCLUDE_TITLE | ADVANCE | EXCLUDE_TA | FRONTIER_PREPRINT | AWAITING_CLASSIFICATION | INCLUDE_A | INCLUDE_B | INCLUDE_A_AND_B | EXCLUDE_FT | RETAIN_BACKGROUND | NOT_RETRIEVED | AWAITING_TRANSLATION | DUPLICATE_RECORD | DUPLICATE_VERSION | NR | NA | UNCLEAR</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -4459,7 +4573,7 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Reconciled full-text disposition (screening_log_template full_text.reconciliation.final_disposition): INCLUDE_A, INCLUDE_B, INCLUDE_A_AND_B, EXCLUDE_FT or an administrative status; maps to scope_stream through vocabulary_crosswalks.scope_stream.from_screening_disposition.</t>
+          <t>Reconciled full-text disposition (screening_log_template full_text.reconciliation.final_disposition): INCLUDE_A, INCLUDE_B, INCLUDE_A_AND_B, EXCLUDE_FT, RETAIN_BACKGROUND or another administrative status; maps to scope_stream through vocabulary_crosswalks.scope_stream.from_screening_disposition. Copy-only; null when no screening record exists.</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -4518,7 +4632,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Canonical v3 field for the single primary full-text exclusion code (first established FT01-FT08 code; 04_screening/fulltext_exclusion_codes.json). Null unless consensus_screening_decision = EXCLUDE_FT; administrative statuses take no code. Supersedes the legacy column reports.exclusion_reason (deprecated alias, kept null).</t>
+          <t>Canonical v3 field for the single primary full-text exclusion code (first established FT01-FT08 code; 04_screening/fulltext_exclusion_codes.json). Null unless consensus_screening_decision = EXCLUDE_FT; administrative statuses (including RETAIN_BACKGROUND) take no code. Supersedes the legacy column reports.exclusion_reason (deprecated alias, kept null). Copy-only.</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -4679,7 +4793,7 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued, "; "): whether the report uses the open-window term, invokes immunosuppression or susceptibility without the term, interprets changes as redistribution, or offers no window interpretation; plus the locator(s) of the source passage. Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.</t>
+          <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued and exhaustive, "; "): authors' own voice only (adopted introduction rationale, discussion, conclusions); one locator per value written "value: locator" (analysis_unit_rules.author_window_interpretation). Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -4730,7 +4844,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued, "; "): whether the report uses the open-window term, invokes immunosuppression or susceptibility without the term, interprets changes as redistribution, or offers no window interpretation; plus the locator(s) of the source passage. Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.</t>
+          <t>Author open-window interpretation (controlled_vocabulary.author_window_interpretation; multi-valued and exhaustive, "; "): authors' own voice only (adopted introduction rationale, discussion, conclusions); one locator per value written "value: locator" (analysis_unit_rules.author_window_interpretation). Charted descriptively under RQ2 (contract 8.3d); never used for eligibility or weighting. no_window_interpretation and NR are not combined with other values.</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -5017,7 +5131,7 @@
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>招募人数</t>
+          <t>招募人数 v3.1: people enrolled before any exclusion in the cohort as the report defines it; when several candidate numbers exist, record the pre-exclusion enrolment and list the others in cohort_notes.</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -5123,11 +5237,19 @@
           <t>enum_or_text</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>untrained_or_sedentary | recreationally_active | trained | elite_or_professional | mixed_training_status | other | NR | NA | UNCLEAR</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>training_status</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>warning (free text allowed)</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -5143,7 +5265,7 @@
       <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>未训练/休闲/训练/精英</t>
+          <t>未训练/休闲/训练/精英 v3.1: controlled_vocabulary.training_status.</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -5269,7 +5391,7 @@
       <c r="J34" s="4" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Free-text notes on the cohort (recruitment source, overlap reasoning with other reports, separable strata) with locators.</t>
+          <t>Free-text notes on the cohort (recruitment source, alternative enrolment figures, overlap reasoning with other reports, separable strata, age-rule derivation) with locators.</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -5320,7 +5442,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Age range and summary exactly as reported (e.g. "18-35 y; mean 24.1 (SD 3.2)"), including any older-adult threshold used by the authors; NR if not reported (unreported age remains awaiting classification at screening, not FT03).</t>
+          <t>Age range and summary exactly as reported (e.g. "18-35 y; mean 24.1 (SD 3.2)"), including any older-adult threshold used by the authors; NR if not reported (unreported or non-qualifying age remains awaiting classification at screening, not FT03; age rule in analysis_unit_rules.population).</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -5379,7 +5501,7 @@
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Adult-population status (controlled_vocabulary.adult_stratum_separable): all participants &gt;= 18 y; mixed-age cohort with a separable adult stratum (eligible; chart that stratum only); mixed-age cohort without a separable adult stratum, or all &lt; 18 y (FT03; appears only in boundary/pilot records).</t>
+          <t>Adult-population status (controlled_vocabulary.adult_stratum_separable) under the age rule (analysis_unit_rules.population: explicit range/minimum &gt;= 18 y or mean - 2*SD &gt;= 18 y): all participants &gt;= 18 y; mixed-age cohort with a separable adult stratum (eligible; chart that stratum only); mixed-age cohort without a separable adult stratum, or all &lt; 18 y (FT03; only when &lt; 18 y participation is stated); UNCLEAR when the rule cannot be applied.</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -5709,7 +5831,7 @@
       <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>该分析有效独立受试者数</t>
+          <t>该分析有效独立受试者数 v3.1: unique participants analysed for the primary immune outcome of this report-cohort link (the immune outcome named first in the aims, else the first immune result reported); other denominators (other outcomes, platforms, subgroups) go to link_notes and to sample_sets.n_participants.</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -5823,7 +5945,7 @@
       <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Free-text justification of the report-study-cohort link (shared registry ID, identical baseline table, author statement) with locators.</t>
+          <t>Free-text justification of the report-study-cohort link (shared registry ID, identical baseline table, author statement) and the other denominators of this report (outcome-, platform- or subgroup-specific n) with locators.</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -5937,7 +6059,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Primary key of sample_sets (one group × assay/matrix × exact timepoint sample set).</t>
+          <t>Primary key of sample_sets (one cohort × group/arm × matrix × time point as sampled in the Methods (whether or not a result is reported for that combination); assay platforms are listed in assay_platform ("; "-separated). Split by platform only when the report gives a platform-specific n that differs between platforms at that time point; split by analysis subgroup only when subgroup n and subgroup results are reported; control-arm time points get their own rows.).</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -6235,11 +6357,19 @@
           <t>enum_or_text</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>endurance | resistance | interval_or_sprint | mixed_or_concurrent | intermittent_team_or_racket_sport | other | NR | NA | UNCLEAR</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>exercise_mode</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>warning (free text allowed)</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -6255,7 +6385,7 @@
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>耐力/抗阻/混合/比赛</t>
+          <t>耐力/抗阻/混合/比赛 v3.1: controlled_vocabulary.exercise_mode (competition coded by its mode).</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -6615,7 +6745,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>pre_exercise_baseline | during_exercise | immediate_post | recovery_post | nonexercise_control | matched_control | other | NR | NA | UNCLEAR</t>
+          <t>pre_exercise_baseline | during_exercise | immediate_post | recovery_post | nonexercise_control | matched_control | periodic_training_monitoring | resting_habitual_group | other | NR | NA | UNCLEAR</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -6692,7 +6822,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>保留原始运动前/中/后时间，不能只留分箱</t>
+          <t>保留原始运动前/中/后时间，不能只留分箱 v3.1: value = earliest stated bound; unit min/h/d (controlled_vocabulary.time_unit); see time_bin_rules.boundary_rules.</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -6755,7 +6885,7 @@
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>保留原始运动前/中/后时间，不能只留分箱</t>
+          <t>保留原始运动前/中/后时间，不能只留分箱 v3.1: value = earliest stated bound; unit min/h/d (controlled_vocabulary.time_unit); see time_bin_rules.boundary_rules.</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -6798,11 +6928,19 @@
           <t>object</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>min | h | d | NR | NA | UNCLEAR</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>time_unit</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>warning (free text allowed)</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -6818,7 +6956,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>保留原始运动前/中/后时间，不能只留分箱</t>
+          <t>保留原始运动前/中/后时间，不能只留分箱 v3.1: value = earliest stated bound; unit min/h/d (controlled_vocabulary.time_unit); see time_bin_rules.boundary_rules.</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -6932,11 +7070,19 @@
           <t>enum_or_text</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>whole_blood | PBMC | sorted_or_isolated_immune_cells | plasma | serum | saliva | urine | sweat | extracellular_vesicles | other_cell_free_biofluid | tissue | other | NR | NA | UNCLEAR</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>matrix</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>warning (free text allowed)</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -6952,7 +7098,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>全血/血浆/血清/PBMC/唾液/尿/汗/组织分别编码</t>
+          <t>全血/血浆/血清/PBMC/唾液/尿/汗/组织分别编码 v3.1: controlled_vocabulary.matrix.</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -7015,7 +7161,7 @@
       <c r="J64" s="4" t="inlineStr"/>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Assay/platform of this sample set (e.g. flow-cytometry panel, ELISA kit, Olink panel, RNA-seq); rows are split when n differs between platforms. Sample-set counterpart of measurements.platform.</t>
+          <t>Assay platform(s) applied to this sample set ("; "-separated, e.g. "flow cytometry; Olink Target 96 Inflammation"); the row is split by platform only when the report gives a platform-specific n that differs. Sample-set counterpart of measurements.platform.</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -7066,7 +7212,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>每组、每平台、每时间点实际人数</t>
+          <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -7129,7 +7275,7 @@
       <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>每组、每平台、每时间点实际人数</t>
+          <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -7192,7 +7338,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>每组、每平台、每时间点实际人数</t>
+          <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -7255,7 +7401,7 @@
       <c r="J68" s="4" t="inlineStr"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>每组、每平台、每时间点实际人数</t>
+          <t>每组、每平台、每时间点实际人数 v3.1: one sample_sets row per cohort × group × matrix × time point; per-platform n recorded separately only when reported (row split by platform).</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -7900,7 +8046,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Free-text notes on the sample set (timing-anchor ambiguity, pooling, exclusions) with locators.</t>
+          <t>Free-text notes on the sample set (timing-anchor ambiguity, pooling, exclusions; flags TIME_BIN_STRADDLE, DAY_LEVEL_TIMING, IMMEDIATE_NONNUMERIC, DERIVED_N) with locators.</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -8171,7 +8317,7 @@
       <c r="J84" s="4" t="inlineStr"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>Basis used to identify/count biological donors and relation to participant IDs.</t>
+          <t>Basis used to identify/count biological donors; only for single-cell, single-nucleus or sorted-cell assays, NA otherwise (values defined in analysis_unit_rules.single_cell).</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -8438,7 +8584,7 @@
       </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>Primary key of measurements (One assay-level tested-universe summary OR one named candidate/feature × comparison; include all named immune candidates from original aims/methods regardless of significance.).</t>
+          <t>Primary key of measurements (Conventional/targeted assays: one named analyte × one author-reported statistical test (one row for a time main effect across time points; one row per time-point contrast only when each contrast is the reported test). Omics: one assay_universe_summary row per analysis universe (platform × matrix × analysis route) plus one named_immune_candidate row per candidate named in the main text, main tables or figure legends; supplementary result tables are summarised in the universe row by counts and locators; candidates prespecified in the original aims/methods are always enumerated (including nulls); set-level results (pathways, modules, hit counts) as one reported_result_summary row per analysis.).</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -10106,7 +10252,7 @@
       <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Distinguish assay-level universe summary from named candidate and reported-result rows; connect rows from one assay universe.</t>
+          <t>record_type (assay_universe_summary / named_immune_candidate / reported_result_summary; definitions in controlled_vocabulary_definitions.measurement_record_type) and assay_universe_id linking named and summary rows to their universe row.</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
@@ -10157,7 +10303,7 @@
       <c r="J118" s="4" t="inlineStr"/>
       <c r="K118" s="4" t="inlineStr">
         <is>
-          <t>Distinguish assay-level universe summary from named candidate and reported-result rows; connect rows from one assay universe.</t>
+          <t>record_type (assay_universe_summary / named_immune_candidate / reported_result_summary; definitions in controlled_vocabulary_definitions.measurement_record_type) and assay_universe_id linking named and summary rows to their universe row.</t>
         </is>
       </c>
       <c r="L118" s="4" t="inlineStr">
@@ -10547,7 +10693,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>all_named_immune_candidates_from_original_aims_methods_regardless_of_significance | complete_targeted_panel | author_reported_feature_set | other_source_defined_rule | NR | NA | UNCLEAR</t>
+          <t>all_named_immune_candidates_from_original_aims_methods_regardless_of_significance | complete_targeted_panel | author_reported_feature_set | statistically_selected_hits_from_untargeted_screen | other_source_defined_rule | NR | NA | UNCLEAR</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -10573,7 +10719,7 @@
       <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
-          <t>Record candidate selection rule, source in original aims/methods/protocol, and timing. Original aims/methods qualify without preregistration.</t>
+          <t>Candidate selection rule, basis and prespecification timing; apply to every non-universe row including conventional targeted assays; prespecification refers to the named candidate, not the platform (controlled_vocabulary_definitions.candidate_fields).</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -10606,7 +10752,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>original_aims | original_methods | registered_protocol_or_analysis_plan | supplement | other | NR | NA | UNCLEAR</t>
+          <t>original_aims | original_methods | registered_protocol_or_analysis_plan | supplement | results_statistical_selection | other | NR | NA | UNCLEAR</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -10632,7 +10778,7 @@
       <c r="J127" s="4" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
-          <t>Record candidate selection rule, source in original aims/methods/protocol, and timing. Original aims/methods qualify without preregistration.</t>
+          <t>Candidate selection rule, basis and prespecification timing; apply to every non-universe row including conventional targeted assays; prespecification refers to the named candidate, not the platform (controlled_vocabulary_definitions.candidate_fields).</t>
         </is>
       </c>
       <c r="L127" s="4" t="inlineStr">
@@ -10691,7 +10837,7 @@
       <c r="J128" s="4" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
-          <t>Record candidate selection rule, source in original aims/methods/protocol, and timing. Original aims/methods qualify without preregistration.</t>
+          <t>Candidate selection rule, basis and prespecification timing; apply to every non-universe row including conventional targeted assays; prespecification refers to the named candidate, not the platform (controlled_vocabulary_definitions.candidate_fields).</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
@@ -10962,7 +11108,7 @@
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr">
         <is>
-          <t>Distinguish explicit null/nonsignificant result from a named candidate whose result was not retrievable or not separately reported.</t>
+          <t>Distinguish explicit null/nonsignificant result from a named candidate whose result was not retrievable or not separately reported; follows the author-reported test and stated threshold (controlled_vocabulary_definitions.result_status).</t>
         </is>
       </c>
       <c r="L133" s="4" t="inlineStr">
@@ -11021,7 +11167,7 @@
       <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L134" s="4" t="inlineStr">
@@ -11072,7 +11218,7 @@
       <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L135" s="4" t="inlineStr">
@@ -11123,7 +11269,7 @@
       <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L136" s="4" t="inlineStr">
@@ -11174,7 +11320,7 @@
       <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
-          <t>Figure and panel from which a value was read (e.g. "Fig. 3B, left"); required when effect_value_source = digitized_from_figure, otherwise NA.</t>
+          <t>Figure and panel showing the result (e.g. "Fig. 3B, left"); filled whenever the result is shown only in a figure (FIGURE_ONLY) and whenever a value is digitized; otherwise NA.</t>
         </is>
       </c>
       <c r="L137" s="4" t="inlineStr">
@@ -11225,7 +11371,7 @@
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
@@ -11276,7 +11422,7 @@
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
@@ -11327,7 +11473,7 @@
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
@@ -11378,7 +11524,7 @@
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
@@ -11429,7 +11575,7 @@
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr">
@@ -11480,7 +11626,7 @@
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>Distinguish author-reported values from digitized figure readings; record the predeclared method, panel, two readings and reconciliation.</t>
+          <t>Origin of effect_value. v3.1: figure-only values are not digitised: effect_value_source NR, digitization fields NA, digitization_check NA, figure_panel_locator filled, flag FIGURE_ONLY (analysis_unit_rules.figure_values).</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
@@ -11513,7 +11659,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>leukocyte_redistribution | NK_count_or_cytotoxicity | neutrophil_function | T_cell_subsets_or_function | mucosal_sIgA | cytokine_or_inflammatory_mediator | immunoglobulin_or_complement | immune_cell_transcriptome | proteome | metabolome_or_lipidome | epigenome | ncRNA | single_cell | other | NR | NA | UNCLEAR</t>
+          <t>leukocyte_redistribution | NK_count_or_cytotoxicity | neutrophil_function | T_cell_subsets_or_function | mucosal_sIgA | mucosal_antimicrobial_protein | cytokine_or_inflammatory_mediator | immunoglobulin_or_complement | immune_cell_transcriptome | proteome | metabolome_or_lipidome | epigenome | ncRNA | single_cell | other | NR | NA | UNCLEAR</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -11539,7 +11685,7 @@
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr">
         <is>
-          <t>Marker family (controlled_vocabulary.marker_family; conventional vs omics classes in vocabulary_crosswalks.marker_family_classes) used to organise Figure 1 and the per-marker validation-readiness map (Figure 2). Assigned per row from the measured analyte/platform, not from author framing.</t>
+          <t>Marker family (controlled_vocabulary.marker_family; conventional vs omics classes in vocabulary_crosswalks.marker_family_classes) used to organise Figure 1 and the per-marker validation-readiness map (Figure 2). Named analytes that map to a conventional family are classified by analyte whatever the platform; omics families for universe/summary rows and features without a conventional family (controlled_vocabulary_definitions.marker_family).</t>
         </is>
       </c>
       <c r="L144" s="4" t="inlineStr">
@@ -11598,7 +11744,7 @@
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr">
         <is>
-          <t>Status of the second-reviewer check of a digitized value (controlled_vocabulary.digitization_check); NA when effect_value_source is not digitized_from_figure.</t>
+          <t>Status of the second-reviewer check of a digitized value (controlled_vocabulary.digitization_check); NA when effect_value_source is not digitized_from_figure (always NA in v3.1: figure values are not digitised).</t>
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr">
@@ -11653,7 +11799,7 @@
       </c>
       <c r="K146" s="4" t="inlineStr">
         <is>
-          <t>Primary key of precision_validation (one report/cohort/measurement × one domain).</t>
+          <t>Primary key of precision_validation (one report × cohort × marker_family × one domain (default: one set of seven domain rows per report × cohort × marker family, measurement_id null); an additional analyte-level row (measurement_id = one measurement ID) only for a domain where the report gives analyte-specific evidence. No rows for background reports.).</t>
         </is>
       </c>
       <c r="L146" s="4" t="inlineStr">
@@ -13041,32 +13187,40 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>extraction_provenance</t>
+          <t>precision_validation</t>
         </is>
       </c>
       <c r="B170" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>provenance_id</t>
+          <t>marker_family</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>identifier</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr"/>
-      <c r="F170" s="4" t="inlineStr"/>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>leukocyte_redistribution | NK_count_or_cytotoxicity | neutrophil_function | T_cell_subsets_or_function | mucosal_sIgA | mucosal_antimicrobial_protein | cytokine_or_inflammatory_mediator | immunoglobulin_or_complement | immune_cell_transcriptome | proteome | metabolome_or_lipidome | epigenome | ncRNA | single_cell | other | NR | NA | UNCLEAR</t>
+        </is>
+      </c>
+      <c r="F170" s="4" t="inlineStr">
+        <is>
+          <t>marker_family</t>
+        </is>
+      </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>strict</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
-          <t>forbidden (identifier)</t>
+          <t>NR/NA/UNCLEAR after source review; blank = not yet extracted</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -13074,19 +13228,15 @@
           <t>Text (@)</t>
         </is>
       </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="J170" s="4" t="inlineStr"/>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>Primary key of extraction_provenance (one report × one extraction/audit event).</t>
+          <t>Marker family (controlled_vocabulary.marker_family) of the domain-row set: one set of seven domain rows per report × cohort × marker family; optional (v3.1, PRE-004), appended as the last column; null on rows created before v3.1.</t>
         </is>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>table_specs.primary_key</t>
+          <t>new_operational_fields_not_in_legacy_61["precision_validation.marker_family"]</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr"/>
@@ -13100,11 +13250,11 @@
         </is>
       </c>
       <c r="B171" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>report_id</t>
+          <t>provenance_id</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -13131,17 +13281,17 @@
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>FK → reports.report_id</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
         <is>
-          <t>Foreign key → reports.report_id.</t>
+          <t>Primary key of extraction_provenance (one report × one extraction/audit event).</t>
         </is>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>table_specs.foreign_keys</t>
+          <t>table_specs.primary_key</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr"/>
@@ -13155,16 +13305,16 @@
         </is>
       </c>
       <c r="B172" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>extractor_a_b.extractor_A</t>
+          <t>report_id</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>string (component of object)</t>
+          <t>identifier</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr"/>
@@ -13176,7 +13326,7 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>NR/NA/UNCLEAR after source review; blank = not yet extracted</t>
+          <t>forbidden (identifier)</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -13184,32 +13334,24 @@
           <t>Text (@)</t>
         </is>
       </c>
-      <c r="J172" s="4" t="inlineStr"/>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>FK → reports.report_id</t>
+        </is>
+      </c>
       <c r="K172" s="4" t="inlineStr">
         <is>
-          <t>两位研究者独立提取记录 — component `extractor_A`</t>
+          <t>Foreign key → reports.report_id.</t>
         </is>
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["extractor_a_b"] (provenance)</t>
-        </is>
-      </c>
-      <c r="M172" s="4" t="inlineStr">
-        <is>
-          <t>extractor_a_b</t>
-        </is>
-      </c>
-      <c r="N172" s="4" t="inlineStr">
-        <is>
-          <t>provenance</t>
-        </is>
-      </c>
-      <c r="O172" s="4" t="inlineStr">
-        <is>
-          <t>After review: NR / NA / UNCLEAR. JSON null in blank_record means not yet extracted.</t>
-        </is>
-      </c>
+          <t>table_specs.foreign_keys</t>
+        </is>
+      </c>
+      <c r="M172" s="4" t="inlineStr"/>
+      <c r="N172" s="4" t="inlineStr"/>
+      <c r="O172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -13218,11 +13360,11 @@
         </is>
       </c>
       <c r="B173" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>extractor_a_b.extractor_B</t>
+          <t>extractor_a_b.extractor_A</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -13250,7 +13392,7 @@
       <c r="J173" s="4" t="inlineStr"/>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>两位研究者独立提取记录 — component `extractor_B`</t>
+          <t>两位研究者独立提取记录 — component `extractor_A`</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
@@ -13281,11 +13423,11 @@
         </is>
       </c>
       <c r="B174" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>extractor_a_b.independent_entry_complete</t>
+          <t>extractor_a_b.extractor_B</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -13313,7 +13455,7 @@
       <c r="J174" s="4" t="inlineStr"/>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>两位研究者独立提取记录 — component `independent_entry_complete`</t>
+          <t>两位研究者独立提取记录 — component `extractor_B`</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
@@ -13344,11 +13486,11 @@
         </is>
       </c>
       <c r="B175" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>extractor_a_b.verification_complete</t>
+          <t>extractor_a_b.independent_entry_complete</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -13376,7 +13518,7 @@
       <c r="J175" s="4" t="inlineStr"/>
       <c r="K175" s="4" t="inlineStr">
         <is>
-          <t>两位研究者独立提取记录 — component `verification_complete`</t>
+          <t>两位研究者独立提取记录 — component `independent_entry_complete`</t>
         </is>
       </c>
       <c r="L175" s="4" t="inlineStr">
@@ -13407,16 +13549,16 @@
         </is>
       </c>
       <c r="B176" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>adjudication</t>
+          <t>extractor_a_b.verification_complete</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>string_or_object</t>
+          <t>string (component of object)</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr"/>
@@ -13439,17 +13581,17 @@
       <c r="J176" s="4" t="inlineStr"/>
       <c r="K176" s="4" t="inlineStr">
         <is>
-          <t>分歧、依据与最终决定</t>
+          <t>两位研究者独立提取记录 — component `verification_complete`</t>
         </is>
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["adjudication"] (provenance)</t>
+          <t>legacy_61_fields["extractor_a_b"] (provenance)</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>adjudication</t>
+          <t>extractor_a_b</t>
         </is>
       </c>
       <c r="N176" s="4" t="inlineStr">
@@ -13470,16 +13612,16 @@
         </is>
       </c>
       <c r="B177" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>ai_assistance.used</t>
+          <t>adjudication</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>string (component of object)</t>
+          <t>string_or_object</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr"/>
@@ -13502,17 +13644,17 @@
       <c r="J177" s="4" t="inlineStr"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
-          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `used`</t>
+          <t>分歧、依据与最终决定</t>
         </is>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["ai_assistance"] (provenance)</t>
+          <t>legacy_61_fields["adjudication"] (provenance)</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>ai_assistance</t>
+          <t>adjudication</t>
         </is>
       </c>
       <c r="N177" s="4" t="inlineStr">
@@ -13533,11 +13675,11 @@
         </is>
       </c>
       <c r="B178" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>ai_assistance.tool_model_date</t>
+          <t>ai_assistance.used</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -13565,7 +13707,7 @@
       <c r="J178" s="4" t="inlineStr"/>
       <c r="K178" s="4" t="inlineStr">
         <is>
-          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `tool_model_date`</t>
+          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `used`</t>
         </is>
       </c>
       <c r="L178" s="4" t="inlineStr">
@@ -13596,11 +13738,11 @@
         </is>
       </c>
       <c r="B179" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>ai_assistance.task_prompt_version</t>
+          <t>ai_assistance.tool_model_date</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -13628,7 +13770,7 @@
       <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `task_prompt_version`</t>
+          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `tool_model_date`</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
@@ -13659,11 +13801,11 @@
         </is>
       </c>
       <c r="B180" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>ai_assistance.output_checked_by_human</t>
+          <t>ai_assistance.task_prompt_version</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -13691,7 +13833,7 @@
       <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
-          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `output_checked_by_human`</t>
+          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `task_prompt_version`</t>
         </is>
       </c>
       <c r="L180" s="4" t="inlineStr">
@@ -13722,16 +13864,16 @@
         </is>
       </c>
       <c r="B181" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>open_data</t>
+          <t>ai_assistance.output_checked_by_human</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>string_or_object</t>
+          <t>string (component of object)</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr"/>
@@ -13754,17 +13896,17 @@
       <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
-          <t>数据集登录号、代码、访问条件与复用许可</t>
+          <t>模型/日期/任务/提示词版本/输出/人工复核 — component `output_checked_by_human`</t>
         </is>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["open_data"] (provenance)</t>
+          <t>legacy_61_fields["ai_assistance"] (provenance)</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>open_data</t>
+          <t>ai_assistance</t>
         </is>
       </c>
       <c r="N181" s="4" t="inlineStr">
@@ -13785,11 +13927,11 @@
         </is>
       </c>
       <c r="B182" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>integrity_status</t>
+          <t>open_data</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -13817,17 +13959,17 @@
       <c r="J182" s="4" t="inlineStr"/>
       <c r="K182" s="4" t="inlineStr">
         <is>
-          <t>出版商/PubMed更正撤稿检查日期及结果，不把未发现写成保证</t>
+          <t>数据集登录号、代码、访问条件与复用许可</t>
         </is>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["integrity_status"] (provenance)</t>
+          <t>legacy_61_fields["open_data"] (provenance)</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>integrity_status</t>
+          <t>open_data</t>
         </is>
       </c>
       <c r="N182" s="4" t="inlineStr">
@@ -13848,16 +13990,16 @@
         </is>
       </c>
       <c r="B183" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>recorded_at</t>
+          <t>integrity_status</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_or_object</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr"/>
@@ -13880,17 +14022,29 @@
       <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
-          <t>Date-time (ISO 8601 with time zone) at which the extraction or audit event was recorded.</t>
+          <t>出版商/PubMed更正撤稿检查日期及结果，不把未发现写成保证</t>
         </is>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>new_operational_fields_not_in_legacy_61["extraction_provenance.recorded_at"]</t>
-        </is>
-      </c>
-      <c r="M183" s="4" t="inlineStr"/>
-      <c r="N183" s="4" t="inlineStr"/>
-      <c r="O183" s="4" t="inlineStr"/>
+          <t>legacy_61_fields["integrity_status"] (provenance)</t>
+        </is>
+      </c>
+      <c r="M183" s="4" t="inlineStr">
+        <is>
+          <t>integrity_status</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="O183" s="4" t="inlineStr">
+        <is>
+          <t>After review: NR / NA / UNCLEAR. JSON null in blank_record means not yet extracted.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -13899,11 +14053,11 @@
         </is>
       </c>
       <c r="B184" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>provenance_notes</t>
+          <t>recorded_at</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -13931,12 +14085,12 @@
       <c r="J184" s="4" t="inlineStr"/>
       <c r="K184" s="4" t="inlineStr">
         <is>
-          <t>Free-text notes on the extraction/audit event (deviations from the manual, access problems, AI-assistance details) with locators.</t>
+          <t>Date-time (ISO 8601 with time zone) at which the extraction or audit event was recorded.</t>
         </is>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>new_operational_fields_not_in_legacy_61["extraction_provenance.provenance_notes"]</t>
+          <t>new_operational_fields_not_in_legacy_61["extraction_provenance.recorded_at"]</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr"/>
@@ -13946,15 +14100,15 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>study_families</t>
+          <t>extraction_provenance</t>
         </is>
       </c>
       <c r="B185" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>provenance_notes</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -13971,7 +14125,7 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>forbidden (identifier)</t>
+          <t>NR/NA/UNCLEAR after source review; blank = not yet extracted</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
@@ -13979,36 +14133,20 @@
           <t>Text (@)</t>
         </is>
       </c>
-      <c r="J185" s="4" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
-          <t>独立研究ID Primary key.</t>
+          <t>Free-text notes on the extraction/audit event (deviations from the manual, access problems, AI-assistance details) with locators.</t>
         </is>
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["study_id"] (identity)</t>
-        </is>
-      </c>
-      <c r="M185" s="4" t="inlineStr">
-        <is>
-          <t>study_id</t>
-        </is>
-      </c>
-      <c r="N185" s="4" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="O185" s="4" t="inlineStr">
-        <is>
-          <t>Assign a stable nonempty unique ID; NR/NA/UNCLEAR are forbidden. JSON null is allowed only in the unfilled blank_record.</t>
-        </is>
-      </c>
+          <t>new_operational_fields_not_in_legacy_61["extraction_provenance.provenance_notes"]</t>
+        </is>
+      </c>
+      <c r="M185" s="4" t="inlineStr"/>
+      <c r="N185" s="4" t="inlineStr"/>
+      <c r="O185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -14017,11 +14155,11 @@
         </is>
       </c>
       <c r="B186" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>study_label</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -14038,7 +14176,7 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>NR/NA/UNCLEAR after source review; blank = not yet extracted</t>
+          <t>forbidden (identifier)</t>
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr">
@@ -14046,20 +14184,36 @@
           <t>Text (@)</t>
         </is>
       </c>
-      <c r="J186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
-          <t>Short human-readable study/trial label (e.g. acronym or programme name); not an identifier.</t>
+          <t>独立研究ID Primary key.</t>
         </is>
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>new_operational_fields_not_in_legacy_61["study_families.study_label"]</t>
-        </is>
-      </c>
-      <c r="M186" s="4" t="inlineStr"/>
-      <c r="N186" s="4" t="inlineStr"/>
-      <c r="O186" s="4" t="inlineStr"/>
+          <t>legacy_61_fields["study_id"] (identity)</t>
+        </is>
+      </c>
+      <c r="M186" s="4" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="O186" s="4" t="inlineStr">
+        <is>
+          <t>Assign a stable nonempty unique ID; NR/NA/UNCLEAR are forbidden. JSON null is allowed only in the unfilled blank_record.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -14068,16 +14222,16 @@
         </is>
       </c>
       <c r="B187" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>design</t>
+          <t>study_label</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>enum_or_text</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr"/>
@@ -14100,29 +14254,17 @@
       <c r="J187" s="4" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
-          <t>随机/交叉/单组前后/前瞻队列/横断面</t>
+          <t>Short human-readable study/trial label (e.g. acronym or programme name); not an identifier.</t>
         </is>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["design"] (exposure)</t>
-        </is>
-      </c>
-      <c r="M187" s="4" t="inlineStr">
-        <is>
-          <t>design</t>
-        </is>
-      </c>
-      <c r="N187" s="4" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="O187" s="4" t="inlineStr">
-        <is>
-          <t>After review: NR / NA / UNCLEAR. JSON null in blank_record means not yet extracted.</t>
-        </is>
-      </c>
+          <t>new_operational_fields_not_in_legacy_61["study_families.study_label"]</t>
+        </is>
+      </c>
+      <c r="M187" s="4" t="inlineStr"/>
+      <c r="N187" s="4" t="inlineStr"/>
+      <c r="O187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -14131,23 +14273,31 @@
         </is>
       </c>
       <c r="B188" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>registry_ids</t>
+          <t>design</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>array</t>
-        </is>
-      </c>
-      <c r="E188" s="4" t="inlineStr"/>
-      <c r="F188" s="4" t="inlineStr"/>
+          <t>enum_or_text</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>randomized_parallel | randomized_crossover | nonrandomized_controlled | nonrandomized_crossover | single_group_pre_post | prospective_cohort | cross_sectional | case_series_or_case_report | other | NR | NA | UNCLEAR</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>warning (free text allowed)</t>
         </is>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -14163,17 +14313,29 @@
       <c r="J188" s="4" t="inlineStr"/>
       <c r="K188" s="4" t="inlineStr">
         <is>
-          <t>Trial or study registry identifiers as reported (e.g. NCT, ISRCTN, ChiCTR, DRKS numbers), "; "-separated; NR if none is reported.</t>
+          <t>随机/交叉/单组前后/前瞻队列/横断面 v3.1: controlled_vocabulary.design.</t>
         </is>
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>new_operational_fields_not_in_legacy_61["study_families.registry_ids"]</t>
-        </is>
-      </c>
-      <c r="M188" s="4" t="inlineStr"/>
-      <c r="N188" s="4" t="inlineStr"/>
-      <c r="O188" s="4" t="inlineStr"/>
+          <t>legacy_61_fields["design"] (exposure)</t>
+        </is>
+      </c>
+      <c r="M188" s="4" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>After review: NR / NA / UNCLEAR. JSON null in blank_record means not yet extracted.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -14182,16 +14344,16 @@
         </is>
       </c>
       <c r="B189" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>training_load</t>
+          <t>registry_ids</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>string_or_object</t>
+          <t>array</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr"/>
@@ -14214,29 +14376,17 @@
       <c r="J189" s="4" t="inlineStr"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
-          <t>先前负荷、训练期与恢复安排</t>
+          <t>Trial or study registry identifiers as reported (e.g. NCT, ISRCTN, ChiCTR, DRKS numbers), "; "-separated; NR if none is reported.</t>
         </is>
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["training_load"] (exposure)</t>
-        </is>
-      </c>
-      <c r="M189" s="4" t="inlineStr">
-        <is>
-          <t>training_load</t>
-        </is>
-      </c>
-      <c r="N189" s="4" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="O189" s="4" t="inlineStr">
-        <is>
-          <t>After review: NR / NA / UNCLEAR. JSON null in blank_record means not yet extracted.</t>
-        </is>
-      </c>
+          <t>new_operational_fields_not_in_legacy_61["study_families.registry_ids"]</t>
+        </is>
+      </c>
+      <c r="M189" s="4" t="inlineStr"/>
+      <c r="N189" s="4" t="inlineStr"/>
+      <c r="O189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -14245,16 +14395,16 @@
         </is>
       </c>
       <c r="B190" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>cointerventions</t>
+          <t>training_load</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>string_or_array</t>
+          <t>string_or_object</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr"/>
@@ -14277,17 +14427,17 @@
       <c r="J190" s="4" t="inlineStr"/>
       <c r="K190" s="4" t="inlineStr">
         <is>
-          <t>营养、补剂、睡眠或其他干预</t>
+          <t>先前负荷、训练期与恢复安排</t>
         </is>
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>legacy_61_fields["cointerventions"] (exposure)</t>
+          <t>legacy_61_fields["training_load"] (exposure)</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>cointerventions</t>
+          <t>training_load</t>
         </is>
       </c>
       <c r="N190" s="4" t="inlineStr">
@@ -14308,16 +14458,16 @@
         </is>
       </c>
       <c r="B191" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>study_notes</t>
+          <t>cointerventions</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_or_array</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr"/>
@@ -14340,21 +14490,84 @@
       <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
+          <t>营养、补剂、睡眠或其他干预</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>legacy_61_fields["cointerventions"] (exposure)</t>
+        </is>
+      </c>
+      <c r="M191" s="4" t="inlineStr">
+        <is>
+          <t>cointerventions</t>
+        </is>
+      </c>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>exposure</t>
+        </is>
+      </c>
+      <c r="O191" s="4" t="inlineStr">
+        <is>
+          <t>After review: NR / NA / UNCLEAR. JSON null in blank_record means not yet extracted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>study_families</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>study_notes</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr"/>
+      <c r="F192" s="4" t="inlineStr"/>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H192" s="4" t="inlineStr">
+        <is>
+          <t>NR/NA/UNCLEAR after source review; blank = not yet extracted</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>Text (@)</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr"/>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
           <t>Free-text notes on the study family (linked protocols, sub-studies, programme history) with locators.</t>
         </is>
       </c>
-      <c r="L191" s="4" t="inlineStr">
+      <c r="L192" s="4" t="inlineStr">
         <is>
           <t>new_operational_fields_not_in_legacy_61["study_families.study_notes"]</t>
         </is>
       </c>
-      <c r="M191" s="4" t="inlineStr"/>
-      <c r="N191" s="4" t="inlineStr"/>
-      <c r="O191" s="4" t="inlineStr"/>
+      <c r="M192" s="4" t="inlineStr"/>
+      <c r="N192" s="4" t="inlineStr"/>
+      <c r="O192" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <autoFilter ref="A1:O191"/>
+  <autoFilter ref="A1:O192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14366,7 +14579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR18"/>
+  <dimension ref="A1:CD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -14404,7 +14617,13 @@
     <col width="28" customWidth="1" min="65" max="65"/>
     <col width="28" customWidth="1" min="67" max="67"/>
     <col width="28" customWidth="1" min="69" max="69"/>
-    <col width="48" customWidth="1" min="70" max="70"/>
+    <col width="28" customWidth="1" min="71" max="71"/>
+    <col width="28" customWidth="1" min="73" max="73"/>
+    <col width="28" customWidth="1" min="75" max="75"/>
+    <col width="28" customWidth="1" min="77" max="77"/>
+    <col width="28" customWidth="1" min="79" max="79"/>
+    <col width="28" customWidth="1" min="81" max="81"/>
+    <col width="48" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14440,150 +14659,180 @@
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
+          <t>cohorts.training_status</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
           <t>cohorts.adult_stratum_separable</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>cohorts.older_adult_subgroup</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>report_cohort_links.scope_streams</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>sample_sets.exercise_mode</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>sample_sets.sample_role</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>sample_sets.time_unit</t>
+        </is>
+      </c>
+      <c r="AA1" s="7" t="inlineStr">
         <is>
           <t>sample_sets.time_bin</t>
         </is>
       </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
+        <is>
+          <t>sample_sets.matrix</t>
+        </is>
+      </c>
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>sample_sets.participant_linkage</t>
         </is>
       </c>
-      <c r="Y1" s="7" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>sample_sets.donor_count_basis</t>
         </is>
       </c>
-      <c r="AA1" s="7" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>sample_sets.within_organising_window</t>
         </is>
       </c>
-      <c r="AC1" s="7" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>measurements.biological_level</t>
         </is>
       </c>
-      <c r="AE1" s="7" t="inlineStr">
+      <c r="AM1" s="7" t="inlineStr">
         <is>
           <t>measurements.omics_integration</t>
         </is>
       </c>
-      <c r="AG1" s="7" t="inlineStr">
+      <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>measurements.result_direction</t>
         </is>
       </c>
-      <c r="AI1" s="7" t="inlineStr">
+      <c r="AQ1" s="7" t="inlineStr">
         <is>
           <t>measurements.record_type</t>
         </is>
       </c>
-      <c r="AK1" s="7" t="inlineStr">
+      <c r="AS1" s="7" t="inlineStr">
         <is>
           <t>measurements.candidate_selection_rule</t>
         </is>
       </c>
-      <c r="AM1" s="7" t="inlineStr">
+      <c r="AU1" s="7" t="inlineStr">
         <is>
           <t>measurements.candidate_selection_basis</t>
         </is>
       </c>
-      <c r="AO1" s="7" t="inlineStr">
+      <c r="AW1" s="7" t="inlineStr">
         <is>
           <t>measurements.candidate_prespecification_status</t>
         </is>
       </c>
-      <c r="AQ1" s="7" t="inlineStr">
+      <c r="AY1" s="7" t="inlineStr">
         <is>
           <t>measurements.supplement_availability</t>
         </is>
       </c>
-      <c r="AS1" s="7" t="inlineStr">
+      <c r="BA1" s="7" t="inlineStr">
         <is>
           <t>measurements.result_status</t>
         </is>
       </c>
-      <c r="AU1" s="7" t="inlineStr">
+      <c r="BC1" s="7" t="inlineStr">
         <is>
           <t>measurements.effect_value_source</t>
         </is>
       </c>
-      <c r="AW1" s="7" t="inlineStr">
+      <c r="BE1" s="7" t="inlineStr">
         <is>
           <t>measurements.marker_family</t>
         </is>
       </c>
-      <c r="AY1" s="7" t="inlineStr">
+      <c r="BG1" s="7" t="inlineStr">
         <is>
           <t>measurements.digitization_check</t>
         </is>
       </c>
-      <c r="BA1" s="7" t="inlineStr">
+      <c r="BI1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.precision_domain</t>
         </is>
       </c>
-      <c r="BC1" s="7" t="inlineStr">
+      <c r="BK1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.evidence_state</t>
         </is>
       </c>
-      <c r="BE1" s="7" t="inlineStr">
+      <c r="BM1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.relationship_tags</t>
         </is>
       </c>
-      <c r="BG1" s="7" t="inlineStr">
+      <c r="BO1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.clinical_endpoint</t>
         </is>
       </c>
-      <c r="BI1" s="7" t="inlineStr">
+      <c r="BQ1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.intended_use</t>
         </is>
       </c>
-      <c r="BK1" s="7" t="inlineStr">
+      <c r="BS1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.linkage_subtype</t>
         </is>
       </c>
-      <c r="BM1" s="7" t="inlineStr">
+      <c r="BU1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.validation_use_subtype</t>
         </is>
       </c>
-      <c r="BO1" s="7" t="inlineStr">
+      <c r="BW1" s="7" t="inlineStr">
         <is>
           <t>precision_validation.validation_split</t>
         </is>
       </c>
-      <c r="BQ1" s="7" t="inlineStr">
+      <c r="BY1" s="7" t="inlineStr">
+        <is>
+          <t>precision_validation.marker_family</t>
+        </is>
+      </c>
+      <c r="CA1" s="7" t="inlineStr">
+        <is>
+          <t>study_families.design</t>
+        </is>
+      </c>
+      <c r="CC1" s="7" t="inlineStr">
         <is>
           <t>missing codes</t>
         </is>
       </c>
-      <c r="BR1" s="7" t="inlineStr">
+      <c r="CD1" s="7" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
@@ -14607,7 +14856,7 @@
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
-          <t>ADVANCE</t>
+          <t>ADVANCE_TO_ABSTRACT</t>
         </is>
       </c>
       <c r="I2" s="9" t="inlineStr">
@@ -14622,150 +14871,180 @@
       </c>
       <c r="M2" s="9" t="inlineStr">
         <is>
+          <t>untrained_or_sedentary</t>
+        </is>
+      </c>
+      <c r="O2" s="9" t="inlineStr">
+        <is>
           <t>all_participants_adult</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
+      <c r="Q2" s="9" t="inlineStr">
         <is>
           <t>older_adult_cohort</t>
         </is>
       </c>
-      <c r="Q2" s="9" t="inlineStr">
+      <c r="S2" s="9" t="inlineStr">
         <is>
           <t>A_core_acute</t>
         </is>
       </c>
-      <c r="S2" s="9" t="inlineStr">
+      <c r="U2" s="9" t="inlineStr">
+        <is>
+          <t>endurance</t>
+        </is>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>pre_exercise_baseline</t>
         </is>
       </c>
-      <c r="U2" s="9" t="inlineStr">
+      <c r="Y2" s="9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="AA2" s="9" t="inlineStr">
         <is>
           <t>pre_exercise_baseline</t>
         </is>
       </c>
-      <c r="W2" s="9" t="inlineStr">
+      <c r="AC2" s="9" t="inlineStr">
+        <is>
+          <t>whole_blood</t>
+        </is>
+      </c>
+      <c r="AE2" s="9" t="inlineStr">
         <is>
           <t>same_participants_identified</t>
         </is>
       </c>
-      <c r="Y2" s="9" t="inlineStr">
+      <c r="AG2" s="9" t="inlineStr">
         <is>
           <t>unique_human_donors</t>
         </is>
       </c>
-      <c r="AA2" s="9" t="inlineStr">
+      <c r="AI2" s="9" t="inlineStr">
         <is>
           <t>within_window</t>
         </is>
       </c>
-      <c r="AC2" s="9" t="inlineStr">
+      <c r="AK2" s="9" t="inlineStr">
         <is>
           <t>cell_count_or_subset</t>
         </is>
       </c>
-      <c r="AE2" s="9" t="inlineStr">
+      <c r="AM2" s="9" t="inlineStr">
         <is>
           <t>single_omics</t>
         </is>
       </c>
-      <c r="AG2" s="9" t="inlineStr">
+      <c r="AO2" s="9" t="inlineStr">
         <is>
           <t>increase</t>
         </is>
       </c>
-      <c r="AI2" s="9" t="inlineStr">
+      <c r="AQ2" s="9" t="inlineStr">
         <is>
           <t>assay_universe_summary</t>
         </is>
       </c>
-      <c r="AK2" s="9" t="inlineStr">
+      <c r="AS2" s="9" t="inlineStr">
         <is>
           <t>all_named_immune_candidates_from_original_aims_methods_regardless_of_significance</t>
         </is>
       </c>
-      <c r="AM2" s="9" t="inlineStr">
+      <c r="AU2" s="9" t="inlineStr">
         <is>
           <t>original_aims</t>
         </is>
       </c>
-      <c r="AO2" s="9" t="inlineStr">
+      <c r="AW2" s="9" t="inlineStr">
         <is>
           <t>registered_protocol_or_analysis_plan</t>
         </is>
       </c>
-      <c r="AQ2" s="9" t="inlineStr">
+      <c r="AY2" s="9" t="inlineStr">
         <is>
           <t>accessible</t>
         </is>
       </c>
-      <c r="AS2" s="9" t="inlineStr">
+      <c r="BA2" s="9" t="inlineStr">
         <is>
           <t>reported_significant</t>
         </is>
       </c>
-      <c r="AU2" s="9" t="inlineStr">
+      <c r="BC2" s="9" t="inlineStr">
         <is>
           <t>reported_main_text_or_table</t>
         </is>
       </c>
-      <c r="AW2" s="9" t="inlineStr">
+      <c r="BE2" s="9" t="inlineStr">
         <is>
           <t>leukocyte_redistribution</t>
         </is>
       </c>
-      <c r="AY2" s="9" t="inlineStr">
+      <c r="BG2" s="9" t="inlineStr">
         <is>
           <t>not_started</t>
         </is>
       </c>
-      <c r="BA2" s="9" t="inlineStr">
+      <c r="BI2" s="9" t="inlineStr">
         <is>
           <t>analytical_reliability</t>
         </is>
       </c>
-      <c r="BC2" s="9" t="inlineStr">
+      <c r="BK2" s="9" t="inlineStr">
         <is>
           <t>evidence_present</t>
         </is>
       </c>
-      <c r="BE2" s="9" t="inlineStr">
+      <c r="BM2" s="9" t="inlineStr">
         <is>
           <t>co_measured_without_association_test</t>
         </is>
       </c>
-      <c r="BG2" s="9" t="inlineStr">
+      <c r="BO2" s="9" t="inlineStr">
         <is>
           <t>none_reported</t>
         </is>
       </c>
-      <c r="BI2" s="9" t="inlineStr">
+      <c r="BQ2" s="9" t="inlineStr">
         <is>
           <t>mechanistic_research</t>
         </is>
       </c>
-      <c r="BK2" s="9" t="inlineStr">
+      <c r="BS2" s="9" t="inlineStr">
         <is>
           <t>direct_functional_evidence</t>
         </is>
       </c>
-      <c r="BM2" s="9" t="inlineStr">
+      <c r="BU2" s="9" t="inlineStr">
         <is>
           <t>independent_cohort_replication</t>
         </is>
       </c>
-      <c r="BO2" s="9" t="inlineStr">
+      <c r="BW2" s="9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BQ2" s="9" t="inlineStr">
+      <c r="BY2" s="9" t="inlineStr">
+        <is>
+          <t>leukocyte_redistribution</t>
+        </is>
+      </c>
+      <c r="CA2" s="9" t="inlineStr">
+        <is>
+          <t>randomized_parallel</t>
+        </is>
+      </c>
+      <c r="CC2" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="BR2" s="9" t="inlineStr">
+      <c r="CD2" s="9" t="inlineStr">
         <is>
           <t>未报告</t>
         </is>
@@ -14789,7 +15068,7 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>EXCLUDE_TA</t>
+          <t>EXCLUDE_TITLE</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
@@ -14804,150 +15083,180 @@
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
+          <t>recreationally_active</t>
+        </is>
+      </c>
+      <c r="O3" s="9" t="inlineStr">
+        <is>
           <t>mixed_age_adult_stratum_separable</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="Q3" s="9" t="inlineStr">
         <is>
           <t>older_adult_stratum_separable</t>
         </is>
       </c>
-      <c r="Q3" s="9" t="inlineStr">
+      <c r="S3" s="9" t="inlineStr">
         <is>
           <t>B_support_repeated_bouts</t>
         </is>
       </c>
-      <c r="S3" s="9" t="inlineStr">
+      <c r="U3" s="9" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>during_exercise</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="Y3" s="9" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="AA3" s="9" t="inlineStr">
         <is>
           <t>during</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="AC3" s="9" t="inlineStr">
+        <is>
+          <t>PBMC</t>
+        </is>
+      </c>
+      <c r="AE3" s="9" t="inlineStr">
         <is>
           <t>same_participants_aggregate_pairing_documented</t>
         </is>
       </c>
-      <c r="Y3" s="9" t="inlineStr">
+      <c r="AG3" s="9" t="inlineStr">
         <is>
           <t>unique_participants_equivalent</t>
         </is>
       </c>
-      <c r="AA3" s="9" t="inlineStr">
+      <c r="AI3" s="9" t="inlineStr">
         <is>
           <t>outside_window_recovery</t>
         </is>
       </c>
-      <c r="AC3" s="9" t="inlineStr">
+      <c r="AK3" s="9" t="inlineStr">
         <is>
           <t>cellular_function</t>
         </is>
       </c>
-      <c r="AE3" s="9" t="inlineStr">
+      <c r="AM3" s="9" t="inlineStr">
         <is>
           <t>multiple_omics_parallel</t>
         </is>
       </c>
-      <c r="AG3" s="9" t="inlineStr">
+      <c r="AO3" s="9" t="inlineStr">
         <is>
           <t>decrease</t>
         </is>
       </c>
-      <c r="AI3" s="9" t="inlineStr">
+      <c r="AQ3" s="9" t="inlineStr">
         <is>
           <t>named_immune_candidate</t>
         </is>
       </c>
-      <c r="AK3" s="9" t="inlineStr">
+      <c r="AS3" s="9" t="inlineStr">
         <is>
           <t>complete_targeted_panel</t>
         </is>
       </c>
-      <c r="AM3" s="9" t="inlineStr">
+      <c r="AU3" s="9" t="inlineStr">
         <is>
           <t>original_methods</t>
         </is>
       </c>
-      <c r="AO3" s="9" t="inlineStr">
+      <c r="AW3" s="9" t="inlineStr">
         <is>
           <t>stated_in_original_aims_or_methods_no_registration_required</t>
         </is>
       </c>
-      <c r="AQ3" s="9" t="inlineStr">
+      <c r="AY3" s="9" t="inlineStr">
         <is>
           <t>linked_but_not_accessible</t>
         </is>
       </c>
-      <c r="AS3" s="9" t="inlineStr">
+      <c r="BA3" s="9" t="inlineStr">
         <is>
           <t>explicitly_reported_non_significant_or_null</t>
         </is>
       </c>
-      <c r="AU3" s="9" t="inlineStr">
+      <c r="BC3" s="9" t="inlineStr">
         <is>
           <t>reported_supplement</t>
         </is>
       </c>
-      <c r="AW3" s="9" t="inlineStr">
+      <c r="BE3" s="9" t="inlineStr">
         <is>
           <t>NK_count_or_cytotoxicity</t>
         </is>
       </c>
-      <c r="AY3" s="9" t="inlineStr">
+      <c r="BG3" s="9" t="inlineStr">
         <is>
           <t>independently_checked_by_second_reviewer</t>
         </is>
       </c>
-      <c r="BA3" s="9" t="inlineStr">
+      <c r="BI3" s="9" t="inlineStr">
         <is>
           <t>temporal_validity</t>
         </is>
       </c>
-      <c r="BC3" s="9" t="inlineStr">
+      <c r="BK3" s="9" t="inlineStr">
         <is>
           <t>measured_null</t>
         </is>
       </c>
-      <c r="BE3" s="9" t="inlineStr">
+      <c r="BM3" s="9" t="inlineStr">
         <is>
           <t>within_cohort_association</t>
         </is>
       </c>
-      <c r="BG3" s="9" t="inlineStr">
+      <c r="BO3" s="9" t="inlineStr">
         <is>
           <t>self_reported_symptoms</t>
         </is>
       </c>
-      <c r="BI3" s="9" t="inlineStr">
+      <c r="BQ3" s="9" t="inlineStr">
         <is>
           <t>acute_response_monitoring</t>
         </is>
       </c>
-      <c r="BK3" s="9" t="inlineStr">
+      <c r="BS3" s="9" t="inlineStr">
         <is>
           <t>functional_assay_association</t>
         </is>
       </c>
-      <c r="BM3" s="9" t="inlineStr">
+      <c r="BU3" s="9" t="inlineStr">
         <is>
           <t>independent_external_model_validation</t>
         </is>
       </c>
-      <c r="BO3" s="9" t="inlineStr">
+      <c r="BW3" s="9" t="inlineStr">
         <is>
           <t>resampling_same_participants</t>
         </is>
       </c>
-      <c r="BQ3" s="9" t="inlineStr">
+      <c r="BY3" s="9" t="inlineStr">
+        <is>
+          <t>NK_count_or_cytotoxicity</t>
+        </is>
+      </c>
+      <c r="CA3" s="9" t="inlineStr">
+        <is>
+          <t>randomized_crossover</t>
+        </is>
+      </c>
+      <c r="CC3" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BR3" s="9" t="inlineStr">
+      <c r="CD3" s="9" t="inlineStr">
         <is>
           <t>不适用</t>
         </is>
@@ -14971,7 +15280,7 @@
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
-          <t>FRONTIER_PREPRINT</t>
+          <t>ADVANCE</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -14986,150 +15295,180 @@
       </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
+          <t>trained</t>
+        </is>
+      </c>
+      <c r="O4" s="9" t="inlineStr">
+        <is>
           <t>mixed_age_adult_stratum_not_separable</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="Q4" s="9" t="inlineStr">
         <is>
           <t>no_older_adult_stratum</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="S4" s="9" t="inlineStr">
         <is>
           <t>background</t>
         </is>
       </c>
-      <c r="S4" s="9" t="inlineStr">
+      <c r="U4" s="9" t="inlineStr">
+        <is>
+          <t>interval_or_sprint</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>immediate_post</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="Y4" s="9" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="AA4" s="9" t="inlineStr">
         <is>
           <t>0_to_lt30min</t>
         </is>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="AC4" s="9" t="inlineStr">
+        <is>
+          <t>sorted_or_isolated_immune_cells</t>
+        </is>
+      </c>
+      <c r="AE4" s="9" t="inlineStr">
         <is>
           <t>some_participant_overlap</t>
         </is>
       </c>
-      <c r="Y4" s="9" t="inlineStr">
+      <c r="AG4" s="9" t="inlineStr">
         <is>
           <t>pooled_or_composite_donor_material</t>
         </is>
       </c>
-      <c r="AA4" s="9" t="inlineStr">
+      <c r="AI4" s="9" t="inlineStr">
         <is>
           <t>pre_exercise_baseline</t>
         </is>
       </c>
-      <c r="AC4" s="9" t="inlineStr">
+      <c r="AK4" s="9" t="inlineStr">
         <is>
           <t>RNA_mRNA</t>
         </is>
       </c>
-      <c r="AE4" s="9" t="inlineStr">
+      <c r="AM4" s="9" t="inlineStr">
         <is>
           <t>integrated_multiomics</t>
         </is>
       </c>
-      <c r="AG4" s="9" t="inlineStr">
+      <c r="AO4" s="9" t="inlineStr">
         <is>
           <t>no_detected_difference</t>
         </is>
       </c>
-      <c r="AI4" s="9" t="inlineStr">
+      <c r="AQ4" s="9" t="inlineStr">
         <is>
           <t>reported_result_summary</t>
         </is>
       </c>
-      <c r="AK4" s="9" t="inlineStr">
+      <c r="AS4" s="9" t="inlineStr">
         <is>
           <t>author_reported_feature_set</t>
         </is>
       </c>
-      <c r="AM4" s="9" t="inlineStr">
+      <c r="AU4" s="9" t="inlineStr">
         <is>
           <t>registered_protocol_or_analysis_plan</t>
         </is>
       </c>
-      <c r="AO4" s="9" t="inlineStr">
+      <c r="AW4" s="9" t="inlineStr">
         <is>
           <t>posthoc_or_results_only</t>
         </is>
       </c>
-      <c r="AQ4" s="9" t="inlineStr">
+      <c r="AY4" s="9" t="inlineStr">
         <is>
           <t>not_listed</t>
         </is>
       </c>
-      <c r="AS4" s="9" t="inlineStr">
+      <c r="BA4" s="9" t="inlineStr">
         <is>
           <t>named_candidate_result_not_located</t>
         </is>
       </c>
-      <c r="AU4" s="9" t="inlineStr">
+      <c r="BC4" s="9" t="inlineStr">
         <is>
           <t>author_provided</t>
         </is>
       </c>
-      <c r="AW4" s="9" t="inlineStr">
+      <c r="BE4" s="9" t="inlineStr">
         <is>
           <t>neutrophil_function</t>
         </is>
       </c>
-      <c r="AY4" s="9" t="inlineStr">
+      <c r="BG4" s="9" t="inlineStr">
         <is>
           <t>discrepancy_reconciled</t>
         </is>
       </c>
-      <c r="BA4" s="9" t="inlineStr">
+      <c r="BI4" s="9" t="inlineStr">
         <is>
           <t>immune_specificity</t>
         </is>
       </c>
-      <c r="BC4" s="9" t="inlineStr">
+      <c r="BK4" s="9" t="inlineStr">
         <is>
           <t>not_demonstrated</t>
         </is>
       </c>
-      <c r="BE4" s="9" t="inlineStr">
+      <c r="BM4" s="9" t="inlineStr">
         <is>
           <t>same_cohort_replication</t>
         </is>
       </c>
-      <c r="BG4" s="9" t="inlineStr">
+      <c r="BO4" s="9" t="inlineStr">
         <is>
           <t>clinician_defined_syndrome</t>
         </is>
       </c>
-      <c r="BI4" s="9" t="inlineStr">
+      <c r="BQ4" s="9" t="inlineStr">
         <is>
           <t>recovery_monitoring</t>
         </is>
       </c>
-      <c r="BK4" s="9" t="inlineStr">
+      <c r="BS4" s="9" t="inlineStr">
         <is>
           <t>clinical_symptom_outcome</t>
         </is>
       </c>
-      <c r="BM4" s="9" t="inlineStr">
+      <c r="BU4" s="9" t="inlineStr">
         <is>
           <t>internal_validation</t>
         </is>
       </c>
-      <c r="BO4" s="9" t="inlineStr">
+      <c r="BW4" s="9" t="inlineStr">
         <is>
           <t>participant_level_holdout_same_cohort</t>
         </is>
       </c>
-      <c r="BQ4" s="9" t="inlineStr">
+      <c r="BY4" s="9" t="inlineStr">
+        <is>
+          <t>neutrophil_function</t>
+        </is>
+      </c>
+      <c r="CA4" s="9" t="inlineStr">
+        <is>
+          <t>nonrandomized_controlled</t>
+        </is>
+      </c>
+      <c r="CC4" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="BR4" s="9" t="inlineStr">
+      <c r="CD4" s="9" t="inlineStr">
         <is>
           <t>全文仍不清楚</t>
         </is>
@@ -15153,7 +15492,7 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>AWAITING_CLASSIFICATION</t>
+          <t>EXCLUDE_TA</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -15168,137 +15507,167 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
+          <t>elite_or_professional</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
           <t>all_participants_under_18</t>
         </is>
       </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="Q5" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="Q5" s="9" t="inlineStr">
+      <c r="S5" s="9" t="inlineStr">
         <is>
           <t>excluded</t>
         </is>
       </c>
-      <c r="S5" s="9" t="inlineStr">
+      <c r="U5" s="9" t="inlineStr">
+        <is>
+          <t>mixed_or_concurrent</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>recovery_post</t>
         </is>
       </c>
-      <c r="U5" s="9" t="inlineStr">
+      <c r="Y5" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AA5" s="9" t="inlineStr">
         <is>
           <t>30min_to_lt3h</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="AC5" s="9" t="inlineStr">
+        <is>
+          <t>plasma</t>
+        </is>
+      </c>
+      <c r="AE5" s="9" t="inlineStr">
         <is>
           <t>different_participants</t>
         </is>
       </c>
-      <c r="Y5" s="9" t="inlineStr">
+      <c r="AG5" s="9" t="inlineStr">
         <is>
           <t>donor_identity_not_resolved</t>
         </is>
       </c>
-      <c r="AA5" s="9" t="inlineStr">
+      <c r="AI5" s="9" t="inlineStr">
         <is>
           <t>matched_control_time</t>
         </is>
       </c>
-      <c r="AC5" s="9" t="inlineStr">
+      <c r="AK5" s="9" t="inlineStr">
         <is>
           <t>RNA_miRNA</t>
         </is>
       </c>
-      <c r="AE5" s="9" t="inlineStr">
+      <c r="AM5" s="9" t="inlineStr">
         <is>
           <t>not_omics</t>
         </is>
       </c>
-      <c r="AG5" s="9" t="inlineStr">
+      <c r="AO5" s="9" t="inlineStr">
         <is>
           <t>mixed_or_inconsistent</t>
         </is>
       </c>
-      <c r="AK5" s="9" t="inlineStr">
-        <is>
-          <t>other_source_defined_rule</t>
-        </is>
-      </c>
-      <c r="AM5" s="9" t="inlineStr">
+      <c r="AS5" s="9" t="inlineStr">
+        <is>
+          <t>statistically_selected_hits_from_untargeted_screen</t>
+        </is>
+      </c>
+      <c r="AU5" s="9" t="inlineStr">
         <is>
           <t>supplement</t>
         </is>
       </c>
-      <c r="AO5" s="9" t="inlineStr">
+      <c r="AW5" s="9" t="inlineStr">
         <is>
           <t>timing_unclear</t>
         </is>
       </c>
-      <c r="AQ5" s="9" t="inlineStr">
+      <c r="AY5" s="9" t="inlineStr">
         <is>
           <t>not_checked</t>
         </is>
       </c>
-      <c r="AS5" s="9" t="inlineStr">
+      <c r="BA5" s="9" t="inlineStr">
         <is>
           <t>assay_universe_only_no_candidate_result_reported</t>
         </is>
       </c>
-      <c r="AU5" s="9" t="inlineStr">
+      <c r="BC5" s="9" t="inlineStr">
         <is>
           <t>digitized_from_figure</t>
         </is>
       </c>
-      <c r="AW5" s="9" t="inlineStr">
+      <c r="BE5" s="9" t="inlineStr">
         <is>
           <t>T_cell_subsets_or_function</t>
         </is>
       </c>
-      <c r="AY5" s="9" t="inlineStr">
+      <c r="BG5" s="9" t="inlineStr">
         <is>
           <t>not_double_checked</t>
         </is>
       </c>
-      <c r="BA5" s="9" t="inlineStr">
+      <c r="BI5" s="9" t="inlineStr">
         <is>
           <t>individualization</t>
         </is>
       </c>
-      <c r="BC5" s="9" t="inlineStr">
+      <c r="BK5" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="BE5" s="9" t="inlineStr">
+      <c r="BM5" s="9" t="inlineStr">
         <is>
           <t>internal_validation_same_participants</t>
         </is>
       </c>
-      <c r="BG5" s="9" t="inlineStr">
+      <c r="BO5" s="9" t="inlineStr">
         <is>
           <t>pathogen_confirmed_infection</t>
         </is>
       </c>
-      <c r="BI5" s="9" t="inlineStr">
+      <c r="BQ5" s="9" t="inlineStr">
         <is>
           <t>training_adaptation_monitoring</t>
         </is>
       </c>
-      <c r="BK5" s="9" t="inlineStr">
+      <c r="BS5" s="9" t="inlineStr">
         <is>
           <t>clinician_defined_outcome</t>
         </is>
       </c>
-      <c r="BM5" s="9" t="inlineStr">
+      <c r="BU5" s="9" t="inlineStr">
         <is>
           <t>prospective_use_or_impact_validation</t>
         </is>
       </c>
-      <c r="BO5" s="9" t="inlineStr">
+      <c r="BW5" s="9" t="inlineStr">
         <is>
           <t>independent_site_or_cohort</t>
+        </is>
+      </c>
+      <c r="BY5" s="9" t="inlineStr">
+        <is>
+          <t>T_cell_subsets_or_function</t>
+        </is>
+      </c>
+      <c r="CA5" s="9" t="inlineStr">
+        <is>
+          <t>nonrandomized_crossover</t>
         </is>
       </c>
     </row>
@@ -15320,7 +15689,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>INCLUDE_A</t>
+          <t>FRONTIER_PREPRINT</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -15335,137 +15704,167 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
+          <t>mixed_training_status</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="O6" s="9" t="inlineStr">
+      <c r="Q6" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="inlineStr">
+      <c r="S6" s="9" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="S6" s="9" t="inlineStr">
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>intermittent_team_or_racket_sport</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>nonexercise_control</t>
         </is>
       </c>
-      <c r="U6" s="9" t="inlineStr">
+      <c r="Y6" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA6" s="9" t="inlineStr">
         <is>
           <t>3h_to_lt24h</t>
         </is>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="AC6" s="9" t="inlineStr">
+        <is>
+          <t>serum</t>
+        </is>
+      </c>
+      <c r="AE6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="Y6" s="9" t="inlineStr">
+      <c r="AG6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AA6" s="9" t="inlineStr">
+      <c r="AI6" s="9" t="inlineStr">
         <is>
           <t>during_exercise_ancillary</t>
         </is>
       </c>
-      <c r="AC6" s="9" t="inlineStr">
+      <c r="AK6" s="9" t="inlineStr">
         <is>
           <t>RNA_lncRNA</t>
         </is>
       </c>
-      <c r="AE6" s="9" t="inlineStr">
+      <c r="AM6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AG6" s="9" t="inlineStr">
+      <c r="AO6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AK6" s="9" t="inlineStr">
+      <c r="AS6" s="9" t="inlineStr">
+        <is>
+          <t>other_source_defined_rule</t>
+        </is>
+      </c>
+      <c r="AU6" s="9" t="inlineStr">
+        <is>
+          <t>results_statistical_selection</t>
+        </is>
+      </c>
+      <c r="AW6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AM6" s="9" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="AO6" s="9" t="inlineStr">
+      <c r="AY6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AQ6" s="9" t="inlineStr">
+      <c r="BA6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AS6" s="9" t="inlineStr">
+      <c r="BC6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AU6" s="9" t="inlineStr">
+      <c r="BE6" s="9" t="inlineStr">
+        <is>
+          <t>mucosal_sIgA</t>
+        </is>
+      </c>
+      <c r="BG6" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AW6" s="9" t="inlineStr">
+      <c r="BI6" s="9" t="inlineStr">
+        <is>
+          <t>functional_clinical_linkage</t>
+        </is>
+      </c>
+      <c r="BK6" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM6" s="9" t="inlineStr">
+        <is>
+          <t>internal_validation_participant_split</t>
+        </is>
+      </c>
+      <c r="BO6" s="9" t="inlineStr">
+        <is>
+          <t>other_clinical_endpoint</t>
+        </is>
+      </c>
+      <c r="BQ6" s="9" t="inlineStr">
+        <is>
+          <t>immune_function_assessment</t>
+        </is>
+      </c>
+      <c r="BS6" s="9" t="inlineStr">
+        <is>
+          <t>pathogen_confirmed_outcome</t>
+        </is>
+      </c>
+      <c r="BU6" s="9" t="inlineStr">
+        <is>
+          <t>implementation_or_field_use_validation</t>
+        </is>
+      </c>
+      <c r="BW6" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="BY6" s="9" t="inlineStr">
         <is>
           <t>mucosal_sIgA</t>
         </is>
       </c>
-      <c r="AY6" s="9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="BA6" s="9" t="inlineStr">
-        <is>
-          <t>functional_clinical_linkage</t>
-        </is>
-      </c>
-      <c r="BC6" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BE6" s="9" t="inlineStr">
-        <is>
-          <t>internal_validation_participant_split</t>
-        </is>
-      </c>
-      <c r="BG6" s="9" t="inlineStr">
-        <is>
-          <t>other_clinical_endpoint</t>
-        </is>
-      </c>
-      <c r="BI6" s="9" t="inlineStr">
-        <is>
-          <t>immune_function_assessment</t>
-        </is>
-      </c>
-      <c r="BK6" s="9" t="inlineStr">
-        <is>
-          <t>pathogen_confirmed_outcome</t>
-        </is>
-      </c>
-      <c r="BM6" s="9" t="inlineStr">
-        <is>
-          <t>implementation_or_field_use_validation</t>
-        </is>
-      </c>
-      <c r="BO6" s="9" t="inlineStr">
-        <is>
-          <t>NR</t>
+      <c r="CA6" s="9" t="inlineStr">
+        <is>
+          <t>single_group_pre_post</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15886,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>INCLUDE_B</t>
+          <t>AWAITING_CLASSIFICATION</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -15502,137 +15901,167 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="S7" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="U7" s="9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>matched_control</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="Y7" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AA7" s="9" t="inlineStr">
         <is>
           <t>24h_to_72h_inclusive</t>
         </is>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="AC7" s="9" t="inlineStr">
+        <is>
+          <t>saliva</t>
+        </is>
+      </c>
+      <c r="AE7" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Y7" s="9" t="inlineStr">
+      <c r="AG7" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AA7" s="9" t="inlineStr">
+      <c r="AI7" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AC7" s="9" t="inlineStr">
+      <c r="AK7" s="9" t="inlineStr">
         <is>
           <t>RNA_circRNA</t>
         </is>
       </c>
-      <c r="AE7" s="9" t="inlineStr">
+      <c r="AM7" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AG7" s="9" t="inlineStr">
+      <c r="AO7" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AK7" s="9" t="inlineStr">
+      <c r="AS7" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AU7" s="9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="AW7" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AM7" s="9" t="inlineStr">
+      <c r="AY7" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA7" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC7" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE7" s="9" t="inlineStr">
+        <is>
+          <t>mucosal_antimicrobial_protein</t>
+        </is>
+      </c>
+      <c r="BG7" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI7" s="9" t="inlineStr">
+        <is>
+          <t>independent_validation_and_use</t>
+        </is>
+      </c>
+      <c r="BK7" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BM7" s="9" t="inlineStr">
+        <is>
+          <t>independent_external_validation</t>
+        </is>
+      </c>
+      <c r="BO7" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AO7" s="9" t="inlineStr">
+      <c r="BQ7" s="9" t="inlineStr">
+        <is>
+          <t>infection_risk_prediction</t>
+        </is>
+      </c>
+      <c r="BS7" s="9" t="inlineStr">
+        <is>
+          <t>combined_functional_and_clinical</t>
+        </is>
+      </c>
+      <c r="BU7" s="9" t="inlineStr">
+        <is>
+          <t>no_validation_or_use_test</t>
+        </is>
+      </c>
+      <c r="BW7" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AQ7" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AS7" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU7" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AW7" s="9" t="inlineStr">
-        <is>
-          <t>cytokine_or_inflammatory_mediator</t>
-        </is>
-      </c>
-      <c r="AY7" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BA7" s="9" t="inlineStr">
-        <is>
-          <t>independent_validation_and_use</t>
-        </is>
-      </c>
-      <c r="BC7" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="BE7" s="9" t="inlineStr">
-        <is>
-          <t>independent_external_validation</t>
-        </is>
-      </c>
-      <c r="BG7" s="9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="BI7" s="9" t="inlineStr">
-        <is>
-          <t>infection_risk_prediction</t>
-        </is>
-      </c>
-      <c r="BK7" s="9" t="inlineStr">
-        <is>
-          <t>combined_functional_and_clinical</t>
-        </is>
-      </c>
-      <c r="BM7" s="9" t="inlineStr">
-        <is>
-          <t>no_validation_or_use_test</t>
-        </is>
-      </c>
-      <c r="BO7" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="BY7" s="9" t="inlineStr">
+        <is>
+          <t>mucosal_antimicrobial_protein</t>
+        </is>
+      </c>
+      <c r="CA7" s="9" t="inlineStr">
+        <is>
+          <t>prospective_cohort</t>
         </is>
       </c>
     </row>
@@ -15654,7 +16083,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>INCLUDE_A_AND_B</t>
+          <t>INCLUDE_A</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -15669,127 +16098,152 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="S8" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="S8" s="9" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
       <c r="U8" s="9" t="inlineStr">
         <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>periodic_training_monitoring</t>
+        </is>
+      </c>
+      <c r="AA8" s="9" t="inlineStr">
+        <is>
           <t>gt72h</t>
         </is>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="AC8" s="9" t="inlineStr">
+        <is>
+          <t>urine</t>
+        </is>
+      </c>
+      <c r="AE8" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="Y8" s="9" t="inlineStr">
+      <c r="AG8" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AA8" s="9" t="inlineStr">
+      <c r="AI8" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AC8" s="9" t="inlineStr">
+      <c r="AK8" s="9" t="inlineStr">
         <is>
           <t>RNA_other</t>
         </is>
       </c>
-      <c r="AE8" s="9" t="inlineStr">
+      <c r="AM8" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AG8" s="9" t="inlineStr">
+      <c r="AO8" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AK8" s="9" t="inlineStr">
+      <c r="AS8" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU8" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AW8" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AM8" s="9" t="inlineStr">
+      <c r="AY8" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BA8" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BC8" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BE8" s="9" t="inlineStr">
+        <is>
+          <t>cytokine_or_inflammatory_mediator</t>
+        </is>
+      </c>
+      <c r="BG8" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BI8" s="9" t="inlineStr">
+        <is>
+          <t>feasibility</t>
+        </is>
+      </c>
+      <c r="BM8" s="9" t="inlineStr">
+        <is>
+          <t>clinical_followup_no_prediction</t>
+        </is>
+      </c>
+      <c r="BO8" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AO8" s="9" t="inlineStr">
+      <c r="BQ8" s="9" t="inlineStr">
+        <is>
+          <t>infection_diagnosis</t>
+        </is>
+      </c>
+      <c r="BS8" s="9" t="inlineStr">
+        <is>
+          <t>no_linkage_evidence</t>
+        </is>
+      </c>
+      <c r="BU8" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="BW8" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AQ8" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AS8" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AU8" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AW8" s="9" t="inlineStr">
-        <is>
-          <t>immunoglobulin_or_complement</t>
-        </is>
-      </c>
-      <c r="AY8" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="BA8" s="9" t="inlineStr">
-        <is>
-          <t>feasibility</t>
-        </is>
-      </c>
-      <c r="BE8" s="9" t="inlineStr">
-        <is>
-          <t>clinical_followup_no_prediction</t>
-        </is>
-      </c>
-      <c r="BG8" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BI8" s="9" t="inlineStr">
-        <is>
-          <t>infection_diagnosis</t>
-        </is>
-      </c>
-      <c r="BK8" s="9" t="inlineStr">
-        <is>
-          <t>no_linkage_evidence</t>
-        </is>
-      </c>
-      <c r="BM8" s="9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="BO8" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
+      <c r="BY8" s="9" t="inlineStr">
+        <is>
+          <t>cytokine_or_inflammatory_mediator</t>
+        </is>
+      </c>
+      <c r="CA8" s="9" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
         </is>
       </c>
     </row>
@@ -15811,7 +16265,7 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>EXCLUDE_FT</t>
+          <t>INCLUDE_B</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -15819,64 +16273,94 @@
           <t>FT08_MIXED_INTERVENTION_NOT_SEPARABLE</t>
         </is>
       </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="S9" s="9" t="inlineStr">
+      <c r="U9" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>resting_habitual_group</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>matched_control_time</t>
+        </is>
+      </c>
+      <c r="AC9" s="9" t="inlineStr">
+        <is>
+          <t>sweat</t>
+        </is>
+      </c>
+      <c r="AI9" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AK9" s="9" t="inlineStr">
+        <is>
+          <t>protein</t>
+        </is>
+      </c>
+      <c r="AS9" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AU9" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE9" s="9" t="inlineStr">
+        <is>
+          <t>immunoglobulin_or_complement</t>
+        </is>
+      </c>
+      <c r="BM9" s="9" t="inlineStr">
+        <is>
+          <t>clinical_prediction_internal</t>
+        </is>
+      </c>
+      <c r="BO9" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BQ9" s="9" t="inlineStr">
+        <is>
+          <t>clinical_decision_support</t>
+        </is>
+      </c>
+      <c r="BS9" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="U9" s="9" t="inlineStr">
-        <is>
-          <t>matched_control_time</t>
-        </is>
-      </c>
-      <c r="AA9" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AC9" s="9" t="inlineStr">
-        <is>
-          <t>protein</t>
-        </is>
-      </c>
-      <c r="AM9" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="AW9" s="9" t="inlineStr">
-        <is>
-          <t>immune_cell_transcriptome</t>
-        </is>
-      </c>
-      <c r="BE9" s="9" t="inlineStr">
-        <is>
-          <t>clinical_prediction_internal</t>
-        </is>
-      </c>
-      <c r="BG9" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="BI9" s="9" t="inlineStr">
-        <is>
-          <t>clinical_decision_support</t>
-        </is>
-      </c>
-      <c r="BK9" s="9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="BM9" s="9" t="inlineStr">
+      <c r="BU9" s="9" t="inlineStr">
         <is>
           <t>NA</t>
+        </is>
+      </c>
+      <c r="BY9" s="9" t="inlineStr">
+        <is>
+          <t>immunoglobulin_or_complement</t>
+        </is>
+      </c>
+      <c r="CA9" s="9" t="inlineStr">
+        <is>
+          <t>case_series_or_case_report</t>
         </is>
       </c>
     </row>
@@ -15893,7 +16377,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>NOT_RETRIEVED</t>
+          <t>INCLUDE_A_AND_B</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -15901,44 +16385,74 @@
           <t>NR</t>
         </is>
       </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="U10" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="AA10" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AC10" s="9" t="inlineStr">
+        <is>
+          <t>extracellular_vesicles</t>
+        </is>
+      </c>
+      <c r="AK10" s="9" t="inlineStr">
+        <is>
+          <t>cytokine_or_immune_mediator</t>
+        </is>
+      </c>
+      <c r="AU10" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BE10" s="9" t="inlineStr">
+        <is>
+          <t>immune_cell_transcriptome</t>
+        </is>
+      </c>
+      <c r="BM10" s="9" t="inlineStr">
+        <is>
+          <t>clinical_prediction_external</t>
+        </is>
+      </c>
+      <c r="BQ10" s="9" t="inlineStr">
+        <is>
+          <t>return_to_training</t>
+        </is>
+      </c>
+      <c r="BS10" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="U10" s="9" t="inlineStr">
-        <is>
-          <t>NR</t>
-        </is>
-      </c>
-      <c r="AC10" s="9" t="inlineStr">
-        <is>
-          <t>cytokine_or_immune_mediator</t>
-        </is>
-      </c>
-      <c r="AW10" s="9" t="inlineStr">
-        <is>
-          <t>proteome</t>
-        </is>
-      </c>
-      <c r="BE10" s="9" t="inlineStr">
-        <is>
-          <t>clinical_prediction_external</t>
-        </is>
-      </c>
-      <c r="BI10" s="9" t="inlineStr">
-        <is>
-          <t>return_to_training</t>
-        </is>
-      </c>
-      <c r="BK10" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BM10" s="9" t="inlineStr">
+      <c r="BU10" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BY10" s="9" t="inlineStr">
+        <is>
+          <t>immune_cell_transcriptome</t>
+        </is>
+      </c>
+      <c r="CA10" s="9" t="inlineStr">
+        <is>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -15955,7 +16469,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>AWAITING_TRANSLATION</t>
+          <t>EXCLUDE_FT</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -15963,39 +16477,54 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="S11" s="9" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="AA11" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AC11" s="9" t="inlineStr">
+        <is>
+          <t>other_cell_free_biofluid</t>
+        </is>
+      </c>
+      <c r="AK11" s="9" t="inlineStr">
+        <is>
+          <t>metabolite</t>
+        </is>
+      </c>
+      <c r="BE11" s="9" t="inlineStr">
+        <is>
+          <t>proteome</t>
+        </is>
+      </c>
+      <c r="BM11" s="9" t="inlineStr">
+        <is>
+          <t>direct_in_vitro_or_ex_vivo_function_test</t>
+        </is>
+      </c>
+      <c r="BQ11" s="9" t="inlineStr">
+        <is>
+          <t>athletic_performance</t>
+        </is>
+      </c>
+      <c r="BS11" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="U11" s="9" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AC11" s="9" t="inlineStr">
-        <is>
-          <t>metabolite</t>
-        </is>
-      </c>
-      <c r="AW11" s="9" t="inlineStr">
-        <is>
-          <t>metabolome_or_lipidome</t>
-        </is>
-      </c>
-      <c r="BE11" s="9" t="inlineStr">
-        <is>
-          <t>direct_in_vitro_or_ex_vivo_function_test</t>
-        </is>
-      </c>
-      <c r="BI11" s="9" t="inlineStr">
-        <is>
-          <t>athletic_performance</t>
-        </is>
-      </c>
-      <c r="BK11" s="9" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
+      <c r="BY11" s="9" t="inlineStr">
+        <is>
+          <t>proteome</t>
+        </is>
+      </c>
+      <c r="CA11" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16541,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>DUPLICATE_RECORD</t>
+          <t>RETAIN_BACKGROUND</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
@@ -16020,29 +16549,49 @@
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="U12" s="9" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AA12" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
       <c r="AC12" s="9" t="inlineStr">
         <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="AK12" s="9" t="inlineStr">
+        <is>
           <t>lipid</t>
         </is>
       </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>epigenome</t>
-        </is>
-      </c>
       <c r="BE12" s="9" t="inlineStr">
         <is>
+          <t>metabolome_or_lipidome</t>
+        </is>
+      </c>
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
           <t>direct_in_vivo_function_test</t>
         </is>
       </c>
-      <c r="BI12" s="9" t="inlineStr">
+      <c r="BQ12" s="9" t="inlineStr">
         <is>
           <t>other</t>
+        </is>
+      </c>
+      <c r="BY12" s="9" t="inlineStr">
+        <is>
+          <t>metabolome_or_lipidome</t>
+        </is>
+      </c>
+      <c r="CA12" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -16054,120 +16603,207 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>DUPLICATE_VERSION</t>
+          <t>NOT_RETRIEVED</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
         </is>
       </c>
       <c r="AC13" s="9" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="AK13" s="9" t="inlineStr">
+        <is>
           <t>DNA_methylation</t>
         </is>
       </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>ncRNA</t>
-        </is>
-      </c>
       <c r="BE13" s="9" t="inlineStr">
         <is>
+          <t>epigenome</t>
+        </is>
+      </c>
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="BI13" s="9" t="inlineStr">
+      <c r="BQ13" s="9" t="inlineStr">
         <is>
           <t>NR</t>
+        </is>
+      </c>
+      <c r="BY13" s="9" t="inlineStr">
+        <is>
+          <t>epigenome</t>
+        </is>
+      </c>
+      <c r="CA13" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="G14" s="9" t="inlineStr">
         <is>
+          <t>AWAITING_TRANSLATION</t>
+        </is>
+      </c>
+      <c r="AC14" s="9" t="inlineStr">
+        <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AC14" s="9" t="inlineStr">
+      <c r="AK14" s="9" t="inlineStr">
         <is>
           <t>chromatin_accessibility</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>single_cell</t>
-        </is>
-      </c>
       <c r="BE14" s="9" t="inlineStr">
         <is>
+          <t>ncRNA</t>
+        </is>
+      </c>
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BI14" s="9" t="inlineStr">
+      <c r="BQ14" s="9" t="inlineStr">
         <is>
           <t>NA</t>
+        </is>
+      </c>
+      <c r="BY14" s="9" t="inlineStr">
+        <is>
+          <t>ncRNA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="G15" s="9" t="inlineStr">
         <is>
+          <t>DUPLICATE_RECORD</t>
+        </is>
+      </c>
+      <c r="AC15" s="9" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AC15" s="9" t="inlineStr">
+      <c r="AK15" s="9" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="AW15" s="9" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
       <c r="BE15" s="9" t="inlineStr">
         <is>
+          <t>single_cell</t>
+        </is>
+      </c>
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="BI15" s="9" t="inlineStr">
+      <c r="BQ15" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BY15" s="9" t="inlineStr">
+        <is>
+          <t>single_cell</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="G16" s="9" t="inlineStr">
         <is>
+          <t>DUPLICATE_VERSION</t>
+        </is>
+      </c>
+      <c r="AC16" s="9" t="inlineStr">
+        <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AC16" s="9" t="inlineStr">
+      <c r="AK16" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-      <c r="AW16" s="9" t="inlineStr">
+      <c r="BE16" s="9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="BY16" s="9" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>NR</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="AC17" s="9" t="inlineStr">
+      <c r="AK17" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
+      <c r="BE17" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="BY17" s="9" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="AC18" s="9" t="inlineStr">
+      <c r="AK18" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
       </c>
-      <c r="AW18" s="9" t="inlineStr">
+      <c r="BE18" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BY18" s="9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BE19" s="9" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="BY19" s="9" t="inlineStr">
         <is>
           <t>UNCLEAR</t>
         </is>
@@ -16354,7 +16990,7 @@
     <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="immune_link" prompt="Choose from codes sheet (immune_link).  Multi: &quot;; &quot;" type="list" errorStyle="warning">
       <formula1>voc_repo_immune_link</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="consensus_screening_decision" prompt="ADVANCE; EXCLUDE_TA; FRONTIER_PREPRINT; AWAITING_CLASSIFICATION; INCLUDE_A; INCLUDE_B; INCLUDE_A_AND_B; EXCLUDE_FT; NOT_RETRIEVED; AWAITING_TRANSLATION; DUPLICATE_RECORD; DUPLICATE_VERSION; NR; NA; UNCLEAR" type="list" errorStyle="warning">
+    <dataValidation sqref="S2:S1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="consensus_screening_decision" prompt="Choose from codes sheet (screening_log_template screening_dispositions)." type="list" errorStyle="warning">
       <formula1>voc_repo_consensus_screening_decision</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="primary_fulltext_exclusion_reas…" prompt="Choose from codes sheet (fulltext_exclusion_codes.json hierarchy)." type="list" errorStyle="warning">
@@ -16458,7 +17094,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A1:L1"/>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." promptTitle="cohort_id" prompt="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." type="custom" errorStyle="stop">
       <formula1>AND(A2&lt;&gt;"NR",A2&lt;&gt;"NA",A2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
@@ -16467,6 +17103,9 @@
     </dataValidation>
     <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="n_recruited" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(E2),AND(E2&gt;=0,E2=INT(E2)),OR(E2="NR",E2="NA",E2="UNCLEAR"))</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="training_status" prompt="untrained_or_sedentary; recreationally_active; trained; elite_or_professional; mixed_training_status; other; NR; NA; UNCLEAR" type="list" errorStyle="warning">
+      <formula1>voc_coho_training_status</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="adult_stratum_separable" prompt="all_participants_adult; mixed_age_adult_stratum_separable; mixed_age_adult_stratum_not_separable; all_participants_under_18; NR; NA; UNCLEAR" type="list" errorStyle="stop">
       <formula1>voc_coho_adult_stratum_separable</formula1>
@@ -16845,7 +17484,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A1:AQ1"/>
-  <dataValidations count="15">
+  <dataValidations count="18">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." promptTitle="sample_set_id" prompt="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." type="custom" errorStyle="stop">
       <formula1>AND(A2&lt;&gt;"NR",A2&lt;&gt;"NA",A2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
@@ -16858,11 +17497,20 @@
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." promptTitle="cohort_id" prompt="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." type="custom" errorStyle="stop">
       <formula1>AND(D2&lt;&gt;"NR",D2&lt;&gt;"NA",D2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="sample_role" prompt="pre_exercise_baseline; during_exercise; immediate_post; recovery_post; nonexercise_control; matched_control; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
+    <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="exercise_mode" prompt="endurance; resistance; interval_or_sprint; mixed_or_concurrent; intermittent_team_or_racket_sport; other; NR; NA; UNCLEAR" type="list" errorStyle="warning">
+      <formula1>voc_samp_exercise_mode</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="sample_role" prompt="pre_exercise_baseline; during_exercise; immediate_post; recovery_post; nonexercise_control; matched_control; periodic_training_monitoring; resting_habitual_group; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
       <formula1>voc_samp_sample_role</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="time_unit" prompt="min; h; d; NR; NA; UNCLEAR" type="list" errorStyle="warning">
+      <formula1>voc_samp_time_unit</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="time_bin" prompt="pre_exercise_baseline; during; 0_to_lt30min; 30min_to_lt3h; 3h_to_lt24h; 24h_to_72h_inclusive; gt72h; matched_control_time; NR; NA; UNCLEAR" type="list" errorStyle="stop">
       <formula1>voc_samp_time_bin</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="matrix" prompt="whole_blood; PBMC; sorted_or_isolated_immune_cells; plasma; serum; saliva; urine; sweat; extracellular_vesicles; other_cell_free_biofluid; tissue; other; NR; NA; UNCLEAR" type="list" errorStyle="warning">
+      <formula1>voc_samp_matrix</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="n_participants" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(T2),AND(T2&gt;=0,T2=INT(T2)),OR(T2="NR",T2="NA",T2="UNCLEAR"))</formula1>
@@ -17293,10 +17941,10 @@
     <dataValidation sqref="AI2:AI1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Integer ≥ 0, or NR/NA/UNCLEAR after source review." promptTitle="feature_total_count" prompt="Integer ≥ 0, or NR/NA/UNCLEAR after source review." type="custom" errorStyle="stop">
       <formula1>IF(ISNUMBER(AI2),AND(AI2&gt;=0,AI2=INT(AI2)),OR(AI2="NR",AI2="NA",AI2="UNCLEAR"))</formula1>
     </dataValidation>
-    <dataValidation sqref="AL2:AL1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_selection_rule" prompt="all_named_immune_candidates_from_original_aims_methods_regardless_of_significance; complete_targeted_panel; author_reported_feature_set; other_source_defined_rule; NR; NA; UNCLEAR" type="list" errorStyle="stop">
+    <dataValidation sqref="AL2:AL1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_selection_rule" prompt="all_named_immune_candidates_from_original_aims_methods_regardless_of_significance; complete_targeted_panel; author_reported_feature_set; statistically_selected_hits_from_untargeted_screen; other_source_defined_rule; NR; NA; UNCLEAR" type="list" errorStyle="stop">
       <formula1>voc_meas_candidate_selection_rule</formula1>
     </dataValidation>
-    <dataValidation sqref="AM2:AM1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_selection_basis" prompt="original_aims; original_methods; registered_protocol_or_analysis_plan; supplement; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
+    <dataValidation sqref="AM2:AM1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_selection_basis" prompt="original_aims; original_methods; registered_protocol_or_analysis_plan; supplement; results_statistical_selection; other; NR; NA; UNCLEAR" type="list" errorStyle="stop">
       <formula1>voc_meas_candidate_selection_basis</formula1>
     </dataValidation>
     <dataValidation sqref="AN2:AN1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="candidate_prespecification_stat…" prompt="registered_protocol_or_analysis_plan; stated_in_original_aims_or_methods_no_registration_required; posthoc_or_results_only; timing_unclear; NR; NA; UNCLEAR" type="list" errorStyle="stop">
@@ -17330,7 +17978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="5" min="1" max="1"/>
@@ -17357,6 +18005,7 @@
     <col width="18" customWidth="1" style="5" min="22" max="22"/>
     <col width="18" customWidth="1" style="5" min="23" max="23"/>
     <col width="18" customWidth="1" style="5" min="24" max="24"/>
+    <col width="18" customWidth="1" style="5" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -17480,11 +18129,16 @@
           <t>validation_split</t>
         </is>
       </c>
+      <c r="Y1" s="7" t="inlineStr">
+        <is>
+          <t>marker_family</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
-  <autoFilter ref="A1:X1"/>
-  <dataValidations count="13">
+  <autoFilter ref="A1:Y1"/>
+  <dataValidations count="14">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." promptTitle="precision_record_id" prompt="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." type="custom" errorStyle="stop">
       <formula1>AND(A2&lt;&gt;"NR",A2&lt;&gt;"NA",A2&lt;&gt;"UNCLEAR")</formula1>
     </dataValidation>
@@ -17524,6 +18178,9 @@
     <dataValidation sqref="X2:X1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="validation_split" prompt="none; resampling_same_participants; participant_level_holdout_same_cohort; independent_site_or_cohort; NR; NA; UNCLEAR" type="list" errorStyle="stop">
       <formula1>voc_prec_validation_split</formula1>
     </dataValidation>
+    <dataValidation sqref="Y2:Y1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Choose a value from the dropdown (codes sheet). Codes come from the JSON templates." promptTitle="marker_family" prompt="Choose from codes sheet (marker_family)." type="list" errorStyle="stop">
+      <formula1>voc_prec_marker_family</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -17709,9 +18366,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A1:G1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." promptTitle="study_id" prompt="Stable non-empty ID; NR/NA/UNCLEAR are forbidden for identifiers." type="custom" errorStyle="stop">
       <formula1>AND(A2&lt;&gt;"NR",A2&lt;&gt;"NA",A2&lt;&gt;"UNCLEAR")</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value not in code list" error="Not a listed code. For multi-valued fields separate codes with &quot;; &quot;. Press Yes to keep." promptTitle="design" prompt="randomized_parallel; randomized_crossover; nonrandomized_controlled; nonrandomized_crossover; single_group_pre_post; prospective_cohort; cross_sectional; case_series_or_case_report; other; NR; NA; UNCLEAR" type="list" errorStyle="warning">
+      <formula1>voc_stud_design</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
